--- a/Python for Project Work SRE_Part 2/ERS/ERS/ERS_Means/SA_el_hor1_mean.xlsx
+++ b/Python for Project Work SRE_Part 2/ERS/ERS/ERS_Means/SA_el_hor1_mean.xlsx
@@ -453,7 +453,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>49.85029980000001</v>
+        <v>5.081580000000001</v>
       </c>
     </row>
     <row r="3">
@@ -464,7 +464,7 @@
         <v>50</v>
       </c>
       <c r="C3" t="n">
-        <v>51.15697666567517</v>
+        <v>5.286142067149687</v>
       </c>
     </row>
     <row r="4">
@@ -475,7 +475,7 @@
         <v>25</v>
       </c>
       <c r="C4" t="n">
-        <v>60.40524101984494</v>
+        <v>6.535910283755699</v>
       </c>
     </row>
     <row r="5">
@@ -486,7 +486,7 @@
         <v>16.66666666666667</v>
       </c>
       <c r="C5" t="n">
-        <v>86.51534071548582</v>
+        <v>9.778948689790262</v>
       </c>
     </row>
     <row r="6">
@@ -497,7 +497,7 @@
         <v>12.5</v>
       </c>
       <c r="C6" t="n">
-        <v>105.4235767209704</v>
+        <v>12.31683211224317</v>
       </c>
     </row>
     <row r="7">
@@ -508,7 +508,7 @@
         <v>10</v>
       </c>
       <c r="C7" t="n">
-        <v>126.5462402100852</v>
+        <v>12.98590856161071</v>
       </c>
     </row>
     <row r="8">
@@ -519,7 +519,7 @@
         <v>8.333333333333334</v>
       </c>
       <c r="C8" t="n">
-        <v>103.8222573120755</v>
+        <v>11.2767652452746</v>
       </c>
     </row>
     <row r="9">
@@ -530,7 +530,7 @@
         <v>7.142857142857142</v>
       </c>
       <c r="C9" t="n">
-        <v>99.76465197815065</v>
+        <v>11.43069636381222</v>
       </c>
     </row>
     <row r="10">
@@ -541,7 +541,7 @@
         <v>6.25</v>
       </c>
       <c r="C10" t="n">
-        <v>114.6446596747868</v>
+        <v>11.6871467348474</v>
       </c>
     </row>
     <row r="11">
@@ -552,7 +552,7 @@
         <v>5.555555555555555</v>
       </c>
       <c r="C11" t="n">
-        <v>114.7376432740767</v>
+        <v>10.44772609514626</v>
       </c>
     </row>
     <row r="12">
@@ -563,7 +563,7 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>110.131964399662</v>
+        <v>9.269515519410685</v>
       </c>
     </row>
     <row r="13">
@@ -574,7 +574,7 @@
         <v>4.545454545454546</v>
       </c>
       <c r="C13" t="n">
-        <v>104.8209632866578</v>
+        <v>9.089161763056564</v>
       </c>
     </row>
     <row r="14">
@@ -585,7 +585,7 @@
         <v>4.166666666666667</v>
       </c>
       <c r="C14" t="n">
-        <v>115.1594934372274</v>
+        <v>8.571428280493647</v>
       </c>
     </row>
     <row r="15">
@@ -596,7 +596,7 @@
         <v>3.846153846153846</v>
       </c>
       <c r="C15" t="n">
-        <v>122.2227925415165</v>
+        <v>8.281476372790323</v>
       </c>
     </row>
     <row r="16">
@@ -607,7 +607,7 @@
         <v>3.571428571428571</v>
       </c>
       <c r="C16" t="n">
-        <v>112.5911712346595</v>
+        <v>7.810427545976233</v>
       </c>
     </row>
     <row r="17">
@@ -618,7 +618,7 @@
         <v>3.333333333333333</v>
       </c>
       <c r="C17" t="n">
-        <v>98.86177475891013</v>
+        <v>7.300582882845362</v>
       </c>
     </row>
     <row r="18">
@@ -629,7 +629,7 @@
         <v>3.125</v>
       </c>
       <c r="C18" t="n">
-        <v>90.25219390951887</v>
+        <v>6.820205692756382</v>
       </c>
     </row>
     <row r="19">
@@ -640,7 +640,7 @@
         <v>2.941176470588235</v>
       </c>
       <c r="C19" t="n">
-        <v>81.92749503577734</v>
+        <v>6.273312829898585</v>
       </c>
     </row>
     <row r="20">
@@ -651,7 +651,7 @@
         <v>2.777777777777778</v>
       </c>
       <c r="C20" t="n">
-        <v>76.52255165394142</v>
+        <v>5.856750043472708</v>
       </c>
     </row>
     <row r="21">
@@ -662,7 +662,7 @@
         <v>2.631578947368421</v>
       </c>
       <c r="C21" t="n">
-        <v>75.24101725505665</v>
+        <v>5.728568225455592</v>
       </c>
     </row>
     <row r="22">
@@ -673,7 +673,7 @@
         <v>2.5</v>
       </c>
       <c r="C22" t="n">
-        <v>75.95795838543732</v>
+        <v>5.576850546699216</v>
       </c>
     </row>
     <row r="23">
@@ -684,7 +684,7 @@
         <v>2.380952380952381</v>
       </c>
       <c r="C23" t="n">
-        <v>73.27621363599903</v>
+        <v>5.308057973774181</v>
       </c>
     </row>
     <row r="24">
@@ -695,7 +695,7 @@
         <v>2.272727272727273</v>
       </c>
       <c r="C24" t="n">
-        <v>74.28794536365598</v>
+        <v>4.84389660972547</v>
       </c>
     </row>
     <row r="25">
@@ -706,7 +706,7 @@
         <v>2.173913043478261</v>
       </c>
       <c r="C25" t="n">
-        <v>73.8349912521286</v>
+        <v>4.417208221451741</v>
       </c>
     </row>
     <row r="26">
@@ -717,7 +717,7 @@
         <v>2.083333333333333</v>
       </c>
       <c r="C26" t="n">
-        <v>65.16485581543925</v>
+        <v>3.98927773799772</v>
       </c>
     </row>
     <row r="27">
@@ -728,7 +728,7 @@
         <v>2</v>
       </c>
       <c r="C27" t="n">
-        <v>57.34210454475978</v>
+        <v>3.612354076963558</v>
       </c>
     </row>
     <row r="28">
@@ -739,7 +739,7 @@
         <v>1.923076923076923</v>
       </c>
       <c r="C28" t="n">
-        <v>51.91162949657267</v>
+        <v>3.366593642029536</v>
       </c>
     </row>
     <row r="29">
@@ -750,7 +750,7 @@
         <v>1.851851851851852</v>
       </c>
       <c r="C29" t="n">
-        <v>43.84937990825926</v>
+        <v>3.14629509327874</v>
       </c>
     </row>
     <row r="30">
@@ -761,7 +761,7 @@
         <v>1.785714285714286</v>
       </c>
       <c r="C30" t="n">
-        <v>36.58586513323479</v>
+        <v>2.930828434478571</v>
       </c>
     </row>
     <row r="31">
@@ -772,7 +772,7 @@
         <v>1.724137931034483</v>
       </c>
       <c r="C31" t="n">
-        <v>32.57561132886972</v>
+        <v>2.709656274360533</v>
       </c>
     </row>
     <row r="32">
@@ -783,7 +783,7 @@
         <v>1.666666666666667</v>
       </c>
       <c r="C32" t="n">
-        <v>30.35568712548127</v>
+        <v>2.516566420294795</v>
       </c>
     </row>
     <row r="33">
@@ -794,7 +794,7 @@
         <v>1.612903225806452</v>
       </c>
       <c r="C33" t="n">
-        <v>28.47052719789959</v>
+        <v>2.36724228171468</v>
       </c>
     </row>
     <row r="34">
@@ -805,7 +805,7 @@
         <v>1.5625</v>
       </c>
       <c r="C34" t="n">
-        <v>26.63420463118379</v>
+        <v>2.249369177884494</v>
       </c>
     </row>
     <row r="35">
@@ -816,7 +816,7 @@
         <v>1.515151515151515</v>
       </c>
       <c r="C35" t="n">
-        <v>24.72536079411586</v>
+        <v>2.111513633980027</v>
       </c>
     </row>
     <row r="36">
@@ -827,7 +827,7 @@
         <v>1.470588235294118</v>
       </c>
       <c r="C36" t="n">
-        <v>23.40388486646001</v>
+        <v>2.021135597417592</v>
       </c>
     </row>
     <row r="37">
@@ -838,7 +838,7 @@
         <v>1.428571428571428</v>
       </c>
       <c r="C37" t="n">
-        <v>22.13076554885854</v>
+        <v>1.940846938831985</v>
       </c>
     </row>
     <row r="38">
@@ -849,7 +849,7 @@
         <v>1.388888888888889</v>
       </c>
       <c r="C38" t="n">
-        <v>20.91747026427054</v>
+        <v>1.863134203946356</v>
       </c>
     </row>
     <row r="39">
@@ -860,7 +860,7 @@
         <v>1.351351351351351</v>
       </c>
       <c r="C39" t="n">
-        <v>19.78955339354084</v>
+        <v>1.776554690254255</v>
       </c>
     </row>
     <row r="40">
@@ -871,7 +871,7 @@
         <v>1.315789473684211</v>
       </c>
       <c r="C40" t="n">
-        <v>18.75575360716199</v>
+        <v>1.682111522269952</v>
       </c>
     </row>
     <row r="41">
@@ -882,7 +882,7 @@
         <v>1.282051282051282</v>
       </c>
       <c r="C41" t="n">
-        <v>17.8902342084928</v>
+        <v>1.586904227545512</v>
       </c>
     </row>
     <row r="42">
@@ -893,7 +893,7 @@
         <v>1.25</v>
       </c>
       <c r="C42" t="n">
-        <v>16.85131523754028</v>
+        <v>1.489355284732105</v>
       </c>
     </row>
     <row r="43">
@@ -904,7 +904,7 @@
         <v>1.219512195121951</v>
       </c>
       <c r="C43" t="n">
-        <v>16.21892574250469</v>
+        <v>1.393046611709097</v>
       </c>
     </row>
     <row r="44">
@@ -915,7 +915,7 @@
         <v>1.19047619047619</v>
       </c>
       <c r="C44" t="n">
-        <v>15.5411790465118</v>
+        <v>1.305073509552884</v>
       </c>
     </row>
     <row r="45">
@@ -926,7 +926,7 @@
         <v>1.162790697674419</v>
       </c>
       <c r="C45" t="n">
-        <v>14.75439145504922</v>
+        <v>1.224845130132348</v>
       </c>
     </row>
     <row r="46">
@@ -937,7 +937,7 @@
         <v>1.136363636363636</v>
       </c>
       <c r="C46" t="n">
-        <v>14.05721508374552</v>
+        <v>1.162645720970263</v>
       </c>
     </row>
     <row r="47">
@@ -948,7 +948,7 @@
         <v>1.111111111111111</v>
       </c>
       <c r="C47" t="n">
-        <v>13.30105575486033</v>
+        <v>1.122549019292612</v>
       </c>
     </row>
     <row r="48">
@@ -959,7 +959,7 @@
         <v>1.08695652173913</v>
       </c>
       <c r="C48" t="n">
-        <v>12.63493696307534</v>
+        <v>1.079264535487909</v>
       </c>
     </row>
     <row r="49">
@@ -970,7 +970,7 @@
         <v>1.063829787234043</v>
       </c>
       <c r="C49" t="n">
-        <v>12.08550650663808</v>
+        <v>1.036513803355574</v>
       </c>
     </row>
     <row r="50">
@@ -981,7 +981,7 @@
         <v>1.041666666666667</v>
       </c>
       <c r="C50" t="n">
-        <v>11.26051185331438</v>
+        <v>0.9881209674849926</v>
       </c>
     </row>
     <row r="51">
@@ -992,7 +992,7 @@
         <v>1.020408163265306</v>
       </c>
       <c r="C51" t="n">
-        <v>10.77890290759843</v>
+        <v>0.9385532722888911</v>
       </c>
     </row>
     <row r="52">
@@ -1003,7 +1003,7 @@
         <v>1</v>
       </c>
       <c r="C52" t="n">
-        <v>10.33553496969246</v>
+        <v>0.8878874888229364</v>
       </c>
     </row>
     <row r="53">
@@ -1014,7 +1014,7 @@
         <v>0.9803921568627451</v>
       </c>
       <c r="C53" t="n">
-        <v>9.846814799148762</v>
+        <v>0.8365559925085988</v>
       </c>
     </row>
     <row r="54">
@@ -1025,7 +1025,7 @@
         <v>0.9615384615384615</v>
       </c>
       <c r="C54" t="n">
-        <v>9.371776099919597</v>
+        <v>0.7888828812466934</v>
       </c>
     </row>
     <row r="55">
@@ -1036,7 +1036,7 @@
         <v>0.9433962264150942</v>
       </c>
       <c r="C55" t="n">
-        <v>9.004283918521434</v>
+        <v>0.7595011709111464</v>
       </c>
     </row>
     <row r="56">
@@ -1047,7 +1047,7 @@
         <v>0.9259259259259258</v>
       </c>
       <c r="C56" t="n">
-        <v>8.616897870414352</v>
+        <v>0.7278742888864074</v>
       </c>
     </row>
     <row r="57">
@@ -1058,7 +1058,7 @@
         <v>0.9090909090909091</v>
       </c>
       <c r="C57" t="n">
-        <v>8.218406940880664</v>
+        <v>0.6948214704778407</v>
       </c>
     </row>
     <row r="58">
@@ -1069,7 +1069,7 @@
         <v>0.8928571428571428</v>
       </c>
       <c r="C58" t="n">
-        <v>7.822601035171853</v>
+        <v>0.6616927523927773</v>
       </c>
     </row>
     <row r="59">
@@ -1080,7 +1080,7 @@
         <v>0.8771929824561403</v>
       </c>
       <c r="C59" t="n">
-        <v>7.570639964827099</v>
+        <v>0.6300163940019244</v>
       </c>
     </row>
     <row r="60">
@@ -1091,7 +1091,7 @@
         <v>0.8620689655172414</v>
       </c>
       <c r="C60" t="n">
-        <v>7.334859753241147</v>
+        <v>0.599890502924929</v>
       </c>
     </row>
     <row r="61">
@@ -1102,7 +1102,7 @@
         <v>0.8474576271186441</v>
       </c>
       <c r="C61" t="n">
-        <v>7.02711910620946</v>
+        <v>0.5712376945757917</v>
       </c>
     </row>
     <row r="62">
@@ -1113,7 +1113,7 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="C62" t="n">
-        <v>6.663675404786146</v>
+        <v>0.5443741453959811</v>
       </c>
     </row>
     <row r="63">
@@ -1124,7 +1124,7 @@
         <v>0.819672131147541</v>
       </c>
       <c r="C63" t="n">
-        <v>6.290488169640017</v>
+        <v>0.5220311361463558</v>
       </c>
     </row>
     <row r="64">
@@ -1135,7 +1135,7 @@
         <v>0.8064516129032259</v>
       </c>
       <c r="C64" t="n">
-        <v>5.9360079515358</v>
+        <v>0.5047598890104078</v>
       </c>
     </row>
     <row r="65">
@@ -1146,7 +1146,7 @@
         <v>0.7936507936507936</v>
       </c>
       <c r="C65" t="n">
-        <v>5.726840807625909</v>
+        <v>0.488448754335759</v>
       </c>
     </row>
     <row r="66">
@@ -1157,7 +1157,7 @@
         <v>0.78125</v>
       </c>
       <c r="C66" t="n">
-        <v>5.531162320172801</v>
+        <v>0.4730098935857296</v>
       </c>
     </row>
     <row r="67">
@@ -1168,7 +1168,7 @@
         <v>0.7692307692307692</v>
       </c>
       <c r="C67" t="n">
-        <v>5.344848842047939</v>
+        <v>0.4582521937248782</v>
       </c>
     </row>
     <row r="68">
@@ -1179,7 +1179,7 @@
         <v>0.7575757575757576</v>
       </c>
       <c r="C68" t="n">
-        <v>5.167187377478387</v>
+        <v>0.4441140512505594</v>
       </c>
     </row>
     <row r="69">
@@ -1190,7 +1190,7 @@
         <v>0.7462686567164178</v>
       </c>
       <c r="C69" t="n">
-        <v>4.997722586866784</v>
+        <v>0.4305617950792087</v>
       </c>
     </row>
     <row r="70">
@@ -1201,7 +1201,7 @@
         <v>0.7352941176470588</v>
       </c>
       <c r="C70" t="n">
-        <v>4.837870065346888</v>
+        <v>0.4177547676127972</v>
       </c>
     </row>
     <row r="71">
@@ -1212,7 +1212,7 @@
         <v>0.7246376811594202</v>
       </c>
       <c r="C71" t="n">
-        <v>4.69291143782721</v>
+        <v>0.4062486249745059</v>
       </c>
     </row>
     <row r="72">
@@ -1223,7 +1223,7 @@
         <v>0.7142857142857142</v>
       </c>
       <c r="C72" t="n">
-        <v>4.559365141035935</v>
+        <v>0.3957073413429483</v>
       </c>
     </row>
     <row r="73">
@@ -1234,7 +1234,7 @@
         <v>0.7042253521126761</v>
       </c>
       <c r="C73" t="n">
-        <v>4.430731596820165</v>
+        <v>0.3857910515995905</v>
       </c>
     </row>
     <row r="74">
@@ -1245,7 +1245,7 @@
         <v>0.6944444444444444</v>
       </c>
       <c r="C74" t="n">
-        <v>4.306725855762314</v>
+        <v>0.3769225679772696</v>
       </c>
     </row>
     <row r="75">
@@ -1256,7 +1256,7 @@
         <v>0.684931506849315</v>
       </c>
       <c r="C75" t="n">
-        <v>4.187421391674628</v>
+        <v>0.3682555588726389</v>
       </c>
     </row>
     <row r="76">
@@ -1267,7 +1267,7 @@
         <v>0.6756756756756757</v>
       </c>
       <c r="C76" t="n">
-        <v>4.073734675058093</v>
+        <v>0.3598440049619399</v>
       </c>
     </row>
     <row r="77">
@@ -1278,7 +1278,7 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="C77" t="n">
-        <v>3.964506338814776</v>
+        <v>0.3516047122650913</v>
       </c>
     </row>
     <row r="78">
@@ -1289,7 +1289,7 @@
         <v>0.6578947368421053</v>
       </c>
       <c r="C78" t="n">
-        <v>3.860040802210035</v>
+        <v>0.3435993943535134</v>
       </c>
     </row>
     <row r="79">
@@ -1300,7 +1300,7 @@
         <v>0.6493506493506493</v>
       </c>
       <c r="C79" t="n">
-        <v>3.760430941337707</v>
+        <v>0.3358640356187488</v>
       </c>
     </row>
     <row r="80">
@@ -1311,7 +1311,7 @@
         <v>0.641025641025641</v>
       </c>
       <c r="C80" t="n">
-        <v>3.665431328942815</v>
+        <v>0.3283963249737318</v>
       </c>
     </row>
     <row r="81">
@@ -1322,7 +1322,7 @@
         <v>0.6329113924050632</v>
       </c>
       <c r="C81" t="n">
-        <v>3.574663474359519</v>
+        <v>0.3211770635613231</v>
       </c>
     </row>
     <row r="82">
@@ -1333,7 +1333,7 @@
         <v>0.625</v>
       </c>
       <c r="C82" t="n">
-        <v>3.487401845723875</v>
+        <v>0.3141550428845276</v>
       </c>
     </row>
     <row r="83">
@@ -1344,7 +1344,7 @@
         <v>0.6172839506172839</v>
       </c>
       <c r="C83" t="n">
-        <v>3.402943549079115</v>
+        <v>0.3072823860747896</v>
       </c>
     </row>
     <row r="84">
@@ -1355,7 +1355,7 @@
         <v>0.6097560975609756</v>
       </c>
       <c r="C84" t="n">
-        <v>3.3206073156698</v>
+        <v>0.3004842008335991</v>
       </c>
     </row>
     <row r="85">
@@ -1366,7 +1366,7 @@
         <v>0.6024096385542168</v>
       </c>
       <c r="C85" t="n">
-        <v>3.239689853515127</v>
+        <v>0.2937002170028967</v>
       </c>
     </row>
     <row r="86">
@@ -1377,7 +1377,7 @@
         <v>0.5952380952380952</v>
       </c>
       <c r="C86" t="n">
-        <v>3.159287332495213</v>
+        <v>0.2868486999942525</v>
       </c>
     </row>
     <row r="87">
@@ -1388,7 +1388,7 @@
         <v>0.5882352941176471</v>
       </c>
       <c r="C87" t="n">
-        <v>3.079368199677587</v>
+        <v>0.2799360479872116</v>
       </c>
     </row>
     <row r="88">
@@ -1399,7 +1399,7 @@
         <v>0.5813953488372093</v>
       </c>
       <c r="C88" t="n">
-        <v>2.999177475232342</v>
+        <v>0.2728942888156106</v>
       </c>
     </row>
     <row r="89">
@@ -1410,7 +1410,7 @@
         <v>0.5747126436781609</v>
       </c>
       <c r="C89" t="n">
-        <v>2.91883104379523</v>
+        <v>0.2666339402799603</v>
       </c>
     </row>
     <row r="90">
@@ -1421,7 +1421,7 @@
         <v>0.5681818181818182</v>
       </c>
       <c r="C90" t="n">
-        <v>2.838246939172609</v>
+        <v>0.260363054356204</v>
       </c>
     </row>
     <row r="91">
@@ -1432,7 +1432,7 @@
         <v>0.5617977528089888</v>
       </c>
       <c r="C91" t="n">
-        <v>2.773105914405569</v>
+        <v>0.2539823145864648</v>
       </c>
     </row>
     <row r="92">
@@ -1443,7 +1443,7 @@
         <v>0.5555555555555556</v>
       </c>
       <c r="C92" t="n">
-        <v>2.718075578460395</v>
+        <v>0.2484231414099346</v>
       </c>
     </row>
     <row r="93">
@@ -1454,7 +1454,7 @@
         <v>0.5494505494505494</v>
       </c>
       <c r="C93" t="n">
-        <v>2.670650147560165</v>
+        <v>0.2435923551591467</v>
       </c>
     </row>
     <row r="94">
@@ -1465,7 +1465,7 @@
         <v>0.5434782608695652</v>
       </c>
       <c r="C94" t="n">
-        <v>2.623543368208484</v>
+        <v>0.2388105267852642</v>
       </c>
     </row>
     <row r="95">
@@ -1476,7 +1476,7 @@
         <v>0.5376344086021505</v>
       </c>
       <c r="C95" t="n">
-        <v>2.573823767783067</v>
+        <v>0.233829149164625</v>
       </c>
     </row>
     <row r="96">
@@ -1487,7 +1487,7 @@
         <v>0.5319148936170213</v>
       </c>
       <c r="C96" t="n">
-        <v>2.521599130541381</v>
+        <v>0.2286756749839349</v>
       </c>
     </row>
     <row r="97">
@@ -1498,7 +1498,7 @@
         <v>0.5263157894736842</v>
       </c>
       <c r="C97" t="n">
-        <v>2.46676034576385</v>
+        <v>0.2233688557815822</v>
       </c>
     </row>
     <row r="98">
@@ -1509,7 +1509,7 @@
         <v>0.5208333333333334</v>
       </c>
       <c r="C98" t="n">
-        <v>2.409457003553712</v>
+        <v>0.2179637535571073</v>
       </c>
     </row>
     <row r="99">
@@ -1520,7 +1520,7 @@
         <v>0.5154639175257733</v>
       </c>
       <c r="C99" t="n">
-        <v>2.350064784159065</v>
+        <v>0.2129231126203859</v>
       </c>
     </row>
     <row r="100">
@@ -1531,7 +1531,7 @@
         <v>0.5102040816326531</v>
       </c>
       <c r="C100" t="n">
-        <v>2.289065092895559</v>
+        <v>0.2081457651315101</v>
       </c>
     </row>
     <row r="101">
@@ -1542,7 +1542,7 @@
         <v>0.5050505050505051</v>
       </c>
       <c r="C101" t="n">
-        <v>2.230347492354075</v>
+        <v>0.2037808647284532</v>
       </c>
     </row>
     <row r="102">
@@ -1553,7 +1553,7 @@
         <v>0.5</v>
       </c>
       <c r="C102" t="n">
-        <v>2.170464393747447</v>
+        <v>0.1994523782479159</v>
       </c>
     </row>
     <row r="103">
@@ -1564,7 +1564,7 @@
         <v>0.495049504950495</v>
       </c>
       <c r="C103" t="n">
-        <v>2.109884210498548</v>
+        <v>0.1951704424566346</v>
       </c>
     </row>
     <row r="104">
@@ -1575,7 +1575,7 @@
         <v>0.4901960784313725</v>
       </c>
       <c r="C104" t="n">
-        <v>2.049087131847411</v>
+        <v>0.1909597328055463</v>
       </c>
     </row>
     <row r="105">
@@ -1586,7 +1586,7 @@
         <v>0.4854368932038835</v>
       </c>
       <c r="C105" t="n">
-        <v>1.988329110807049</v>
+        <v>0.1868174725788629</v>
       </c>
     </row>
     <row r="106">
@@ -1597,7 +1597,7 @@
         <v>0.4807692307692307</v>
       </c>
       <c r="C106" t="n">
-        <v>1.938885489557895</v>
+        <v>0.1827598291622584</v>
       </c>
     </row>
     <row r="107">
@@ -1608,7 +1608,7 @@
         <v>0.4761904761904762</v>
       </c>
       <c r="C107" t="n">
-        <v>1.90750742986867</v>
+        <v>0.1788219073334709</v>
       </c>
     </row>
     <row r="108">
@@ -1619,7 +1619,7 @@
         <v>0.4716981132075471</v>
       </c>
       <c r="C108" t="n">
-        <v>1.883018379507083</v>
+        <v>0.1752117999992869</v>
       </c>
     </row>
     <row r="109">
@@ -1630,7 +1630,7 @@
         <v>0.4672897196261682</v>
       </c>
       <c r="C109" t="n">
-        <v>1.863019248093299</v>
+        <v>0.1722049687809217</v>
       </c>
     </row>
     <row r="110">
@@ -1641,7 +1641,7 @@
         <v>0.4629629629629629</v>
       </c>
       <c r="C110" t="n">
-        <v>1.842098321721592</v>
+        <v>0.1692556922490758</v>
       </c>
     </row>
     <row r="111">
@@ -1652,7 +1652,7 @@
         <v>0.4587155963302752</v>
       </c>
       <c r="C111" t="n">
-        <v>1.820246769598416</v>
+        <v>0.1663627275397943</v>
       </c>
     </row>
     <row r="112">
@@ -1663,7 +1663,7 @@
         <v>0.4545454545454545</v>
       </c>
       <c r="C112" t="n">
-        <v>1.797508094828198</v>
+        <v>0.1635269979728668</v>
       </c>
     </row>
     <row r="113">
@@ -1674,7 +1674,7 @@
         <v>0.4504504504504504</v>
       </c>
       <c r="C113" t="n">
-        <v>1.773903769230964</v>
+        <v>0.1607445539834969</v>
       </c>
     </row>
     <row r="114">
@@ -1685,7 +1685,7 @@
         <v>0.4464285714285714</v>
       </c>
       <c r="C114" t="n">
-        <v>1.751965374083221</v>
+        <v>0.1582652410985019</v>
       </c>
     </row>
     <row r="115">
@@ -1696,7 +1696,7 @@
         <v>0.4424778761061947</v>
       </c>
       <c r="C115" t="n">
-        <v>1.729552743523994</v>
+        <v>0.1558605970338312</v>
       </c>
     </row>
     <row r="116">
@@ -1707,7 +1707,7 @@
         <v>0.4385964912280702</v>
       </c>
       <c r="C116" t="n">
-        <v>1.706606770607113</v>
+        <v>0.1535027535770318</v>
       </c>
     </row>
     <row r="117">
@@ -1718,7 +1718,7 @@
         <v>0.4347826086956521</v>
       </c>
       <c r="C117" t="n">
-        <v>1.68308593205444</v>
+        <v>0.15118835410168</v>
       </c>
     </row>
     <row r="118">
@@ -1729,7 +1729,7 @@
         <v>0.4310344827586207</v>
       </c>
       <c r="C118" t="n">
-        <v>1.659071967600643</v>
+        <v>0.1489142083247394</v>
       </c>
     </row>
     <row r="119">
@@ -1740,7 +1740,7 @@
         <v>0.4273504273504274</v>
       </c>
       <c r="C119" t="n">
-        <v>1.634647919104999</v>
+        <v>0.1466773404329423</v>
       </c>
     </row>
     <row r="120">
@@ -1751,7 +1751,7 @@
         <v>0.4237288135593221</v>
       </c>
       <c r="C120" t="n">
-        <v>1.609895871418775</v>
+        <v>0.1444750257303262</v>
       </c>
     </row>
     <row r="121">
@@ -1762,7 +1762,7 @@
         <v>0.4201680672268908</v>
       </c>
       <c r="C121" t="n">
-        <v>1.584895177215783</v>
+        <v>0.1423048163358011</v>
       </c>
     </row>
     <row r="122">
@@ -1773,7 +1773,7 @@
         <v>0.4166666666666667</v>
       </c>
       <c r="C122" t="n">
-        <v>1.559721132646809</v>
+        <v>0.1401645568157199</v>
       </c>
     </row>
     <row r="123">
@@ -1784,7 +1784,7 @@
         <v>0.4132231404958678</v>
       </c>
       <c r="C123" t="n">
-        <v>1.534444058009957</v>
+        <v>0.1380523907790873</v>
       </c>
     </row>
     <row r="124">
@@ -1795,7 +1795,7 @@
         <v>0.4098360655737705</v>
       </c>
       <c r="C124" t="n">
-        <v>1.509128730727691</v>
+        <v>0.1359667595986543</v>
       </c>
     </row>
     <row r="125">
@@ -1806,7 +1806,7 @@
         <v>0.4065040650406504</v>
       </c>
       <c r="C125" t="n">
-        <v>1.483834114542192</v>
+        <v>0.133906394448163</v>
       </c>
     </row>
     <row r="126">
@@ -1817,7 +1817,7 @@
         <v>0.4032258064516129</v>
       </c>
       <c r="C126" t="n">
-        <v>1.458613329279633</v>
+        <v>0.1318703028606193</v>
       </c>
     </row>
     <row r="127">
@@ -1828,7 +1828,7 @@
         <v>0.4</v>
       </c>
       <c r="C127" t="n">
-        <v>1.433552835858255</v>
+        <v>0.1298577509429833</v>
       </c>
     </row>
     <row r="128">
@@ -1839,7 +1839,7 @@
         <v>0.3968253968253968</v>
       </c>
       <c r="C128" t="n">
-        <v>1.408648537137308</v>
+        <v>0.127868242335915</v>
       </c>
     </row>
     <row r="129">
@@ -1850,7 +1850,7 @@
         <v>0.3937007874015748</v>
       </c>
       <c r="C129" t="n">
-        <v>1.383937538033192</v>
+        <v>0.1259014948923251</v>
       </c>
     </row>
     <row r="130">
@@ -1861,7 +1861,7 @@
         <v>0.390625</v>
       </c>
       <c r="C130" t="n">
-        <v>1.35945283645925</v>
+        <v>0.1239574159489016</v>
       </c>
     </row>
     <row r="131">
@@ -1872,7 +1872,7 @@
         <v>0.3875968992248062</v>
       </c>
       <c r="C131" t="n">
-        <v>1.335223344790777</v>
+        <v>0.1220360769573922</v>
       </c>
     </row>
     <row r="132">
@@ -1883,7 +1883,7 @@
         <v>0.3846153846153846</v>
       </c>
       <c r="C132" t="n">
-        <v>1.311274360882326</v>
+        <v>0.1201376881295523</v>
       </c>
     </row>
     <row r="133">
@@ -1894,7 +1894,7 @@
         <v>0.3816793893129771</v>
       </c>
       <c r="C133" t="n">
-        <v>1.287634498350235</v>
+        <v>0.1182632335955778</v>
       </c>
     </row>
     <row r="134">
@@ -1905,7 +1905,7 @@
         <v>0.3787878787878788</v>
       </c>
       <c r="C134" t="n">
-        <v>1.264324355292854</v>
+        <v>0.116413249010805</v>
       </c>
     </row>
     <row r="135">
@@ -1916,7 +1916,7 @@
         <v>0.3759398496240601</v>
       </c>
       <c r="C135" t="n">
-        <v>1.241353026222692</v>
+        <v>0.1145874040002402</v>
       </c>
     </row>
     <row r="136">
@@ -1927,7 +1927,7 @@
         <v>0.3731343283582089</v>
       </c>
       <c r="C136" t="n">
-        <v>1.218735577999792</v>
+        <v>0.1127862277857479</v>
       </c>
     </row>
     <row r="137">
@@ -1938,7 +1938,7 @@
         <v>0.3703703703703703</v>
       </c>
       <c r="C137" t="n">
-        <v>1.196675601669347</v>
+        <v>0.1110296687645092</v>
       </c>
     </row>
     <row r="138">
@@ -1949,7 +1949,7 @@
         <v>0.3676470588235294</v>
       </c>
       <c r="C138" t="n">
-        <v>1.178443609693486</v>
+        <v>0.109644475714052</v>
       </c>
     </row>
     <row r="139">
@@ -1960,7 +1960,7 @@
         <v>0.364963503649635</v>
       </c>
       <c r="C139" t="n">
-        <v>1.159726565768598</v>
+        <v>0.1081965193463174</v>
       </c>
     </row>
     <row r="140">
@@ -1971,7 +1971,7 @@
         <v>0.3623188405797101</v>
       </c>
       <c r="C140" t="n">
-        <v>1.140451863294876</v>
+        <v>0.106678062290122</v>
       </c>
     </row>
     <row r="141">
@@ -1982,7 +1982,7 @@
         <v>0.3597122302158273</v>
       </c>
       <c r="C141" t="n">
-        <v>1.125052934410106</v>
+        <v>0.1055406720452814</v>
       </c>
     </row>
     <row r="142">
@@ -1993,7 +1993,7 @@
         <v>0.3571428571428571</v>
       </c>
       <c r="C142" t="n">
-        <v>1.112355659479063</v>
+        <v>0.1044610046290322</v>
       </c>
     </row>
     <row r="143">
@@ -2004,7 +2004,7 @@
         <v>0.3546099290780142</v>
       </c>
       <c r="C143" t="n">
-        <v>1.10103758369505</v>
+        <v>0.1033179944862136</v>
       </c>
     </row>
     <row r="144">
@@ -2015,7 +2015,7 @@
         <v>0.3521126760563381</v>
       </c>
       <c r="C144" t="n">
-        <v>1.08892928197812</v>
+        <v>0.102097562314969</v>
       </c>
     </row>
     <row r="145">
@@ -2026,7 +2026,7 @@
         <v>0.3496503496503497</v>
       </c>
       <c r="C145" t="n">
-        <v>1.07600520371642</v>
+        <v>0.1007972251017134</v>
       </c>
     </row>
     <row r="146">
@@ -2037,7 +2037,7 @@
         <v>0.3472222222222222</v>
       </c>
       <c r="C146" t="n">
-        <v>1.062351651628393</v>
+        <v>0.09942860356042886</v>
       </c>
     </row>
     <row r="147">
@@ -2048,7 +2048,7 @@
         <v>0.3448275862068966</v>
       </c>
       <c r="C147" t="n">
-        <v>1.048907284043995</v>
+        <v>0.09808665569421468</v>
       </c>
     </row>
     <row r="148">
@@ -2059,7 +2059,7 @@
         <v>0.3424657534246575</v>
       </c>
       <c r="C148" t="n">
-        <v>1.037183984245768</v>
+        <v>0.09692340623827432</v>
       </c>
     </row>
     <row r="149">
@@ -2070,7 +2070,7 @@
         <v>0.3401360544217687</v>
       </c>
       <c r="C149" t="n">
-        <v>1.025236803908182</v>
+        <v>0.09574055272043196</v>
       </c>
     </row>
     <row r="150">
@@ -2081,7 +2081,7 @@
         <v>0.3378378378378378</v>
       </c>
       <c r="C150" t="n">
-        <v>1.013057884470122</v>
+        <v>0.09453722392001827</v>
       </c>
     </row>
     <row r="151">
@@ -2092,7 +2092,7 @@
         <v>0.3355704697986577</v>
       </c>
       <c r="C151" t="n">
-        <v>1.000672346518671</v>
+        <v>0.09331588490345062</v>
       </c>
     </row>
     <row r="152">
@@ -2103,7 +2103,7 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="C152" t="n">
-        <v>0.9881282503858039</v>
+        <v>0.09208131738692649</v>
       </c>
     </row>
     <row r="153">
@@ -2114,7 +2114,7 @@
         <v>0.3311258278145696</v>
       </c>
       <c r="C153" t="n">
-        <v>0.9754746280484364</v>
+        <v>0.09083838387936648</v>
       </c>
     </row>
     <row r="154">
@@ -2125,7 +2125,7 @@
         <v>0.3289473684210527</v>
       </c>
       <c r="C154" t="n">
-        <v>0.9627439059648503</v>
+        <v>0.08959023917843505</v>
       </c>
     </row>
     <row r="155">
@@ -2136,7 +2136,7 @@
         <v>0.326797385620915</v>
       </c>
       <c r="C155" t="n">
-        <v>0.9499304407154164</v>
+        <v>0.08833614536745282</v>
       </c>
     </row>
     <row r="156">
@@ -2147,7 +2147,7 @@
         <v>0.3246753246753247</v>
       </c>
       <c r="C156" t="n">
-        <v>0.9370688813749035</v>
+        <v>0.08707946258117298</v>
       </c>
     </row>
     <row r="157">
@@ -2158,7 +2158,7 @@
         <v>0.3225806451612903</v>
       </c>
       <c r="C157" t="n">
-        <v>0.9241935208442038</v>
+        <v>0.08582350792270468</v>
       </c>
     </row>
     <row r="158">
@@ -2169,7 +2169,7 @@
         <v>0.3205128205128205</v>
       </c>
       <c r="C158" t="n">
-        <v>0.9113588743327152</v>
+        <v>0.08457365544149673</v>
       </c>
     </row>
     <row r="159">
@@ -2180,7 +2180,7 @@
         <v>0.3184713375796178</v>
       </c>
       <c r="C159" t="n">
-        <v>0.9014013810624661</v>
+        <v>0.08361885720821981</v>
       </c>
     </row>
     <row r="160">
@@ -2191,7 +2191,7 @@
         <v>0.3164556962025316</v>
       </c>
       <c r="C160" t="n">
-        <v>0.8913977065824142</v>
+        <v>0.08266093181574016</v>
       </c>
     </row>
     <row r="161">
@@ -2202,7 +2202,7 @@
         <v>0.3144654088050314</v>
       </c>
       <c r="C161" t="n">
-        <v>0.8811587829310683</v>
+        <v>0.08168042125695821</v>
       </c>
     </row>
     <row r="162">
@@ -2213,7 +2213,7 @@
         <v>0.3125</v>
       </c>
       <c r="C162" t="n">
-        <v>0.8707215774330409</v>
+        <v>0.08068091127742209</v>
       </c>
     </row>
     <row r="163">
@@ -2224,7 +2224,7 @@
         <v>0.3105590062111801</v>
       </c>
       <c r="C163" t="n">
-        <v>0.8601241235074825</v>
+        <v>0.0796660999612562</v>
       </c>
     </row>
     <row r="164">
@@ -2235,7 +2235,7 @@
         <v>0.308641975308642</v>
       </c>
       <c r="C164" t="n">
-        <v>0.8494052494247391</v>
+        <v>0.07863977113466911</v>
       </c>
     </row>
     <row r="165">
@@ -2246,7 +2246,7 @@
         <v>0.3067484662576687</v>
       </c>
       <c r="C165" t="n">
-        <v>0.8386360688943506</v>
+        <v>0.07760900530176011</v>
       </c>
     </row>
     <row r="166">
@@ -2257,7 +2257,7 @@
         <v>0.3048780487804878</v>
       </c>
       <c r="C166" t="n">
-        <v>0.8278158254734584</v>
+        <v>0.07657356309897242</v>
       </c>
     </row>
     <row r="167">
@@ -2268,7 +2268,7 @@
         <v>0.303030303030303</v>
       </c>
       <c r="C167" t="n">
-        <v>0.8184479597769774</v>
+        <v>0.07568654514175942</v>
       </c>
     </row>
     <row r="168">
@@ -2279,7 +2279,7 @@
         <v>0.3012048192771084</v>
       </c>
       <c r="C168" t="n">
-        <v>0.8091555601207965</v>
+        <v>0.07480744557394932</v>
       </c>
     </row>
     <row r="169">
@@ -2290,7 +2290,7 @@
         <v>0.2994011976047904</v>
       </c>
       <c r="C169" t="n">
-        <v>0.7998655687187033</v>
+        <v>0.07392851134146984</v>
       </c>
     </row>
     <row r="170">
@@ -2301,7 +2301,7 @@
         <v>0.2976190476190476</v>
       </c>
       <c r="C170" t="n">
-        <v>0.7906505990628284</v>
+        <v>0.07305339393687152</v>
       </c>
     </row>
     <row r="171">
@@ -2312,7 +2312,7 @@
         <v>0.2958579881656805</v>
       </c>
       <c r="C171" t="n">
-        <v>0.7814887792650078</v>
+        <v>0.07218164011221968</v>
       </c>
     </row>
     <row r="172">
@@ -2323,7 +2323,7 @@
         <v>0.2941176470588235</v>
       </c>
       <c r="C172" t="n">
-        <v>0.7723964100819084</v>
+        <v>0.07133591890131052</v>
       </c>
     </row>
     <row r="173">
@@ -2334,7 +2334,7 @@
         <v>0.2923976608187134</v>
       </c>
       <c r="C173" t="n">
-        <v>0.7633698607954139</v>
+        <v>0.07055173821010322</v>
       </c>
     </row>
     <row r="174">
@@ -2345,7 +2345,7 @@
         <v>0.2906976744186047</v>
       </c>
       <c r="C174" t="n">
-        <v>0.7544232821809128</v>
+        <v>0.06977256238698004</v>
       </c>
     </row>
     <row r="175">
@@ -2356,7 +2356,7 @@
         <v>0.2890173410404624</v>
       </c>
       <c r="C175" t="n">
-        <v>0.7456393729674328</v>
+        <v>0.06900682624636252</v>
       </c>
     </row>
     <row r="176">
@@ -2367,7 +2367,7 @@
         <v>0.2873563218390804</v>
       </c>
       <c r="C176" t="n">
-        <v>0.7375333552659051</v>
+        <v>0.06830705784960493</v>
       </c>
     </row>
     <row r="177">
@@ -2378,7 +2378,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="C177" t="n">
-        <v>0.7295262236627401</v>
+        <v>0.06761424652964712</v>
       </c>
     </row>
     <row r="178">
@@ -2389,7 +2389,7 @@
         <v>0.2840909090909091</v>
       </c>
       <c r="C178" t="n">
-        <v>0.7216215188968457</v>
+        <v>0.06692876789991536</v>
       </c>
     </row>
     <row r="179">
@@ -2400,7 +2400,7 @@
         <v>0.2824858757062147</v>
       </c>
       <c r="C179" t="n">
-        <v>0.7138223214512132</v>
+        <v>0.06625095407456022</v>
       </c>
     </row>
     <row r="180">
@@ -2411,7 +2411,7 @@
         <v>0.2808988764044944</v>
       </c>
       <c r="C180" t="n">
-        <v>0.7061312580072449</v>
+        <v>0.0655810943061403</v>
       </c>
     </row>
     <row r="181">
@@ -2422,7 +2422,7 @@
         <v>0.2793296089385475</v>
       </c>
       <c r="C181" t="n">
-        <v>0.6985505118754797</v>
+        <v>0.06492113540179939</v>
       </c>
     </row>
     <row r="182">
@@ -2433,7 +2433,7 @@
         <v>0.2777777777777778</v>
       </c>
       <c r="C182" t="n">
-        <v>0.6910818370288988</v>
+        <v>0.06427085105299293</v>
       </c>
     </row>
     <row r="183">
@@ -2444,7 +2444,7 @@
         <v>0.2762430939226519</v>
       </c>
       <c r="C183" t="n">
-        <v>0.6837265749310839</v>
+        <v>0.06362907538329887</v>
       </c>
     </row>
     <row r="184">
@@ -2455,7 +2455,7 @@
         <v>0.2747252747252747</v>
       </c>
       <c r="C184" t="n">
-        <v>0.6764856737983204</v>
+        <v>0.06299594113166986</v>
       </c>
     </row>
     <row r="185">
@@ -2466,7 +2466,7 @@
         <v>0.273224043715847</v>
       </c>
       <c r="C185" t="n">
-        <v>0.6693597095918372</v>
+        <v>0.06237154592880156</v>
       </c>
     </row>
     <row r="186">
@@ -2477,7 +2477,7 @@
         <v>0.2717391304347826</v>
       </c>
       <c r="C186" t="n">
-        <v>0.6623489084678319</v>
+        <v>0.0617559544242881</v>
       </c>
     </row>
     <row r="187">
@@ -2488,7 +2488,7 @@
         <v>0.2702702702702702</v>
       </c>
       <c r="C187" t="n">
-        <v>0.6554531701795934</v>
+        <v>0.06114920049897857</v>
       </c>
     </row>
     <row r="188">
@@ -2499,7 +2499,7 @@
         <v>0.2688172043010753</v>
       </c>
       <c r="C188" t="n">
-        <v>0.648681020840468</v>
+        <v>0.06055219970168047</v>
       </c>
     </row>
     <row r="189">
@@ -2510,7 +2510,7 @@
         <v>0.267379679144385</v>
       </c>
       <c r="C189" t="n">
-        <v>0.6422080625413404</v>
+        <v>0.05998290091107172</v>
       </c>
     </row>
     <row r="190">
@@ -2521,7 +2521,7 @@
         <v>0.2659574468085106</v>
       </c>
       <c r="C190" t="n">
-        <v>0.6358439832397612</v>
+        <v>0.05942195484047339</v>
       </c>
     </row>
     <row r="191">
@@ -2532,7 +2532,7 @@
         <v>0.2645502645502645</v>
       </c>
       <c r="C191" t="n">
-        <v>0.6295871738868984</v>
+        <v>0.0588692497429374</v>
       </c>
     </row>
     <row r="192">
@@ -2543,7 +2543,7 @@
         <v>0.2631578947368421</v>
       </c>
       <c r="C192" t="n">
-        <v>0.6234360012454775</v>
+        <v>0.05832467297804519</v>
       </c>
     </row>
     <row r="193">
@@ -2554,7 +2554,7 @@
         <v>0.2617801047120419</v>
       </c>
       <c r="C193" t="n">
-        <v>0.6173888114518835</v>
+        <v>0.05778811118553442</v>
       </c>
     </row>
     <row r="194">
@@ -2565,7 +2565,7 @@
         <v>0.2604166666666667</v>
       </c>
       <c r="C194" t="n">
-        <v>0.6114439334290868</v>
+        <v>0.05725945045075741</v>
       </c>
     </row>
     <row r="195">
@@ -2576,7 +2576,7 @@
         <v>0.2590673575129534</v>
       </c>
       <c r="C195" t="n">
-        <v>0.605599682196453</v>
+        <v>0.05673857646160876</v>
       </c>
     </row>
     <row r="196">
@@ -2587,7 +2587,7 @@
         <v>0.2577319587628866</v>
       </c>
       <c r="C196" t="n">
-        <v>0.5998543619786236</v>
+        <v>0.05622537465032558</v>
       </c>
     </row>
     <row r="197">
@@ -2598,7 +2598,7 @@
         <v>0.2564102564102564</v>
       </c>
       <c r="C197" t="n">
-        <v>0.594206269275583</v>
+        <v>0.05571973033755419</v>
       </c>
     </row>
     <row r="198">
@@ -2609,7 +2609,7 @@
         <v>0.2551020408163265</v>
       </c>
       <c r="C198" t="n">
-        <v>0.5886614198193262</v>
+        <v>0.05522231623174437</v>
       </c>
     </row>
     <row r="199">
@@ -2620,7 +2620,7 @@
         <v>0.2538071065989848</v>
       </c>
       <c r="C199" t="n">
-        <v>0.5843470441152536</v>
+        <v>0.05473389461395585</v>
       </c>
     </row>
     <row r="200">
@@ -2631,7 +2631,7 @@
         <v>0.2525252525252525</v>
       </c>
       <c r="C200" t="n">
-        <v>0.5805287386816023</v>
+        <v>0.05425264032072735</v>
       </c>
     </row>
     <row r="201">
@@ -2642,7 +2642,7 @@
         <v>0.2512562814070352</v>
       </c>
       <c r="C201" t="n">
-        <v>0.576772938767755</v>
+        <v>0.05377844043252767</v>
       </c>
     </row>
     <row r="202">
@@ -2653,7 +2653,7 @@
         <v>0.25</v>
       </c>
       <c r="C202" t="n">
-        <v>0.5730766715038559</v>
+        <v>0.05331118246351823</v>
       </c>
     </row>
   </sheetData>

--- a/Python for Project Work SRE_Part 2/ERS/ERS/ERS_Means/SA_el_hor1_mean.xlsx
+++ b/Python for Project Work SRE_Part 2/ERS/ERS/ERS_Means/SA_el_hor1_mean.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -464,7 +464,7 @@
         <v>50</v>
       </c>
       <c r="C3" t="n">
-        <v>5.286142067149687</v>
+        <v>5.149764880902457</v>
       </c>
     </row>
     <row r="4">
@@ -475,7 +475,7 @@
         <v>25</v>
       </c>
       <c r="C4" t="n">
-        <v>6.535910283755699</v>
+        <v>5.480278356573172</v>
       </c>
     </row>
     <row r="5">
@@ -486,7 +486,7 @@
         <v>16.66666666666667</v>
       </c>
       <c r="C5" t="n">
-        <v>9.778948689790262</v>
+        <v>6.30353963901543</v>
       </c>
     </row>
     <row r="6">
@@ -497,7 +497,7 @@
         <v>12.5</v>
       </c>
       <c r="C6" t="n">
-        <v>12.31683211224317</v>
+        <v>7.572250483386243</v>
       </c>
     </row>
     <row r="7">
@@ -508,7 +508,7 @@
         <v>10</v>
       </c>
       <c r="C7" t="n">
-        <v>12.98590856161071</v>
+        <v>8.739743924642159</v>
       </c>
     </row>
     <row r="8">
@@ -519,7 +519,7 @@
         <v>8.333333333333334</v>
       </c>
       <c r="C8" t="n">
-        <v>11.2767652452746</v>
+        <v>10.74926585713837</v>
       </c>
     </row>
     <row r="9">
@@ -530,7 +530,7 @@
         <v>7.142857142857142</v>
       </c>
       <c r="C9" t="n">
-        <v>11.43069636381222</v>
+        <v>11.67012151851182</v>
       </c>
     </row>
     <row r="10">
@@ -541,7 +541,7 @@
         <v>6.25</v>
       </c>
       <c r="C10" t="n">
-        <v>11.6871467348474</v>
+        <v>11.52624685708802</v>
       </c>
     </row>
     <row r="11">
@@ -552,7 +552,7 @@
         <v>5.555555555555555</v>
       </c>
       <c r="C11" t="n">
-        <v>10.44772609514626</v>
+        <v>12.71231452894861</v>
       </c>
     </row>
     <row r="12">
@@ -563,7 +563,7 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>9.269515519410685</v>
+        <v>12.22939888769194</v>
       </c>
     </row>
     <row r="13">
@@ -574,7 +574,7 @@
         <v>4.545454545454546</v>
       </c>
       <c r="C13" t="n">
-        <v>9.089161763056564</v>
+        <v>11.76302350518593</v>
       </c>
     </row>
     <row r="14">
@@ -585,7 +585,7 @@
         <v>4.166666666666667</v>
       </c>
       <c r="C14" t="n">
-        <v>8.571428280493647</v>
+        <v>12.67366601453373</v>
       </c>
     </row>
     <row r="15">
@@ -596,7 +596,7 @@
         <v>3.846153846153846</v>
       </c>
       <c r="C15" t="n">
-        <v>8.281476372790323</v>
+        <v>12.64076174942862</v>
       </c>
     </row>
     <row r="16">
@@ -607,7 +607,7 @@
         <v>3.571428571428571</v>
       </c>
       <c r="C16" t="n">
-        <v>7.810427545976233</v>
+        <v>11.75980427234178</v>
       </c>
     </row>
     <row r="17">
@@ -618,7 +618,7 @@
         <v>3.333333333333333</v>
       </c>
       <c r="C17" t="n">
-        <v>7.300582882845362</v>
+        <v>11.35932473255418</v>
       </c>
     </row>
     <row r="18">
@@ -629,7 +629,7 @@
         <v>3.125</v>
       </c>
       <c r="C18" t="n">
-        <v>6.820205692756382</v>
+        <v>11.16384655628082</v>
       </c>
     </row>
     <row r="19">
@@ -640,7 +640,7 @@
         <v>2.941176470588235</v>
       </c>
       <c r="C19" t="n">
-        <v>6.273312829898585</v>
+        <v>10.6572630691823</v>
       </c>
     </row>
     <row r="20">
@@ -651,7 +651,7 @@
         <v>2.777777777777778</v>
       </c>
       <c r="C20" t="n">
-        <v>5.856750043472708</v>
+        <v>10.27899352009469</v>
       </c>
     </row>
     <row r="21">
@@ -662,7 +662,7 @@
         <v>2.631578947368421</v>
       </c>
       <c r="C21" t="n">
-        <v>5.728568225455592</v>
+        <v>9.955218872679737</v>
       </c>
     </row>
     <row r="22">
@@ -673,7 +673,7 @@
         <v>2.5</v>
       </c>
       <c r="C22" t="n">
-        <v>5.576850546699216</v>
+        <v>9.854550289889035</v>
       </c>
     </row>
     <row r="23">
@@ -684,7 +684,7 @@
         <v>2.380952380952381</v>
       </c>
       <c r="C23" t="n">
-        <v>5.308057973774181</v>
+        <v>9.382039721357918</v>
       </c>
     </row>
     <row r="24">
@@ -695,7 +695,7 @@
         <v>2.272727272727273</v>
       </c>
       <c r="C24" t="n">
-        <v>4.84389660972547</v>
+        <v>9.412850336030745</v>
       </c>
     </row>
     <row r="25">
@@ -706,7 +706,7 @@
         <v>2.173913043478261</v>
       </c>
       <c r="C25" t="n">
-        <v>4.417208221451741</v>
+        <v>9.252892988423248</v>
       </c>
     </row>
     <row r="26">
@@ -717,7 +717,7 @@
         <v>2.083333333333333</v>
       </c>
       <c r="C26" t="n">
-        <v>3.98927773799772</v>
+        <v>8.305040963417381</v>
       </c>
     </row>
     <row r="27">
@@ -728,7 +728,7 @@
         <v>2</v>
       </c>
       <c r="C27" t="n">
-        <v>3.612354076963558</v>
+        <v>7.481876198553166</v>
       </c>
     </row>
     <row r="28">
@@ -739,7 +739,7 @@
         <v>1.923076923076923</v>
       </c>
       <c r="C28" t="n">
-        <v>3.366593642029536</v>
+        <v>6.865773066183914</v>
       </c>
     </row>
     <row r="29">
@@ -750,7 +750,7 @@
         <v>1.851851851851852</v>
       </c>
       <c r="C29" t="n">
-        <v>3.14629509327874</v>
+        <v>6.059656843608845</v>
       </c>
     </row>
     <row r="30">
@@ -761,7 +761,7 @@
         <v>1.785714285714286</v>
       </c>
       <c r="C30" t="n">
-        <v>2.930828434478571</v>
+        <v>5.305121598032979</v>
       </c>
     </row>
     <row r="31">
@@ -772,7 +772,7 @@
         <v>1.724137931034483</v>
       </c>
       <c r="C31" t="n">
-        <v>2.709656274360533</v>
+        <v>4.700416587775391</v>
       </c>
     </row>
     <row r="32">
@@ -783,7 +783,7 @@
         <v>1.666666666666667</v>
       </c>
       <c r="C32" t="n">
-        <v>2.516566420294795</v>
+        <v>4.207997827626266</v>
       </c>
     </row>
     <row r="33">
@@ -794,7 +794,7 @@
         <v>1.612903225806452</v>
       </c>
       <c r="C33" t="n">
-        <v>2.36724228171468</v>
+        <v>3.839312872949</v>
       </c>
     </row>
     <row r="34">
@@ -805,7 +805,7 @@
         <v>1.5625</v>
       </c>
       <c r="C34" t="n">
-        <v>2.249369177884494</v>
+        <v>3.536666768140282</v>
       </c>
     </row>
     <row r="35">
@@ -816,7 +816,7 @@
         <v>1.515151515151515</v>
       </c>
       <c r="C35" t="n">
-        <v>2.111513633980027</v>
+        <v>3.213274111439399</v>
       </c>
     </row>
     <row r="36">
@@ -827,7 +827,7 @@
         <v>1.470588235294118</v>
       </c>
       <c r="C36" t="n">
-        <v>2.021135597417592</v>
+        <v>2.952020597772227</v>
       </c>
     </row>
     <row r="37">
@@ -838,7 +838,7 @@
         <v>1.428571428571428</v>
       </c>
       <c r="C37" t="n">
-        <v>1.940846938831985</v>
+        <v>2.759451393610161</v>
       </c>
     </row>
     <row r="38">
@@ -849,7 +849,7 @@
         <v>1.388888888888889</v>
       </c>
       <c r="C38" t="n">
-        <v>1.863134203946356</v>
+        <v>2.689434164739204</v>
       </c>
     </row>
     <row r="39">
@@ -860,7 +860,7 @@
         <v>1.351351351351351</v>
       </c>
       <c r="C39" t="n">
-        <v>1.776554690254255</v>
+        <v>2.657882859701669</v>
       </c>
     </row>
     <row r="40">
@@ -871,7 +871,7 @@
         <v>1.315789473684211</v>
       </c>
       <c r="C40" t="n">
-        <v>1.682111522269952</v>
+        <v>2.572008329932573</v>
       </c>
     </row>
     <row r="41">
@@ -882,7 +882,7 @@
         <v>1.282051282051282</v>
       </c>
       <c r="C41" t="n">
-        <v>1.586904227545512</v>
+        <v>2.398711183731234</v>
       </c>
     </row>
     <row r="42">
@@ -893,7 +893,7 @@
         <v>1.25</v>
       </c>
       <c r="C42" t="n">
-        <v>1.489355284732105</v>
+        <v>2.135956343085045</v>
       </c>
     </row>
     <row r="43">
@@ -904,7 +904,7 @@
         <v>1.219512195121951</v>
       </c>
       <c r="C43" t="n">
-        <v>1.393046611709097</v>
+        <v>1.957334103593813</v>
       </c>
     </row>
     <row r="44">
@@ -915,7 +915,7 @@
         <v>1.19047619047619</v>
       </c>
       <c r="C44" t="n">
-        <v>1.305073509552884</v>
+        <v>1.837520847293675</v>
       </c>
     </row>
     <row r="45">
@@ -926,7 +926,7 @@
         <v>1.162790697674419</v>
       </c>
       <c r="C45" t="n">
-        <v>1.224845130132348</v>
+        <v>1.733737274204429</v>
       </c>
     </row>
     <row r="46">
@@ -937,7 +937,7 @@
         <v>1.136363636363636</v>
       </c>
       <c r="C46" t="n">
-        <v>1.162645720970263</v>
+        <v>1.637896245435789</v>
       </c>
     </row>
     <row r="47">
@@ -948,7 +948,7 @@
         <v>1.111111111111111</v>
       </c>
       <c r="C47" t="n">
-        <v>1.122549019292612</v>
+        <v>1.555936353271191</v>
       </c>
     </row>
     <row r="48">
@@ -959,7 +959,7 @@
         <v>1.08695652173913</v>
       </c>
       <c r="C48" t="n">
-        <v>1.079264535487909</v>
+        <v>1.493657427408387</v>
       </c>
     </row>
     <row r="49">
@@ -970,7 +970,7 @@
         <v>1.063829787234043</v>
       </c>
       <c r="C49" t="n">
-        <v>1.036513803355574</v>
+        <v>1.449639302873169</v>
       </c>
     </row>
     <row r="50">
@@ -981,7 +981,7 @@
         <v>1.041666666666667</v>
       </c>
       <c r="C50" t="n">
-        <v>0.9881209674849926</v>
+        <v>1.345671787146385</v>
       </c>
     </row>
     <row r="51">
@@ -992,7 +992,7 @@
         <v>1.020408163265306</v>
       </c>
       <c r="C51" t="n">
-        <v>0.9385532722888911</v>
+        <v>1.264080080261172</v>
       </c>
     </row>
     <row r="52">
@@ -1003,7 +1003,7 @@
         <v>1</v>
       </c>
       <c r="C52" t="n">
-        <v>0.8878874888229364</v>
+        <v>1.20180267506601</v>
       </c>
     </row>
     <row r="53">
@@ -1014,7 +1014,7 @@
         <v>0.9803921568627451</v>
       </c>
       <c r="C53" t="n">
-        <v>0.8365559925085988</v>
+        <v>1.132865858948054</v>
       </c>
     </row>
     <row r="54">
@@ -1025,7 +1025,7 @@
         <v>0.9615384615384615</v>
       </c>
       <c r="C54" t="n">
-        <v>0.7888828812466934</v>
+        <v>1.068388444486188</v>
       </c>
     </row>
     <row r="55">
@@ -1036,7 +1036,7 @@
         <v>0.9433962264150942</v>
       </c>
       <c r="C55" t="n">
-        <v>0.7595011709111464</v>
+        <v>1.020772869127159</v>
       </c>
     </row>
     <row r="56">
@@ -1047,7 +1047,7 @@
         <v>0.9259259259259258</v>
       </c>
       <c r="C56" t="n">
-        <v>0.7278742888864074</v>
+        <v>0.9757826668364362</v>
       </c>
     </row>
     <row r="57">
@@ -1058,7 +1058,7 @@
         <v>0.9090909090909091</v>
       </c>
       <c r="C57" t="n">
-        <v>0.6948214704778407</v>
+        <v>0.936767082790669</v>
       </c>
     </row>
     <row r="58">
@@ -1069,7 +1069,7 @@
         <v>0.8928571428571428</v>
       </c>
       <c r="C58" t="n">
-        <v>0.6616927523927773</v>
+        <v>0.9167479193475222</v>
       </c>
     </row>
     <row r="59">
@@ -1080,7 +1080,7 @@
         <v>0.8771929824561403</v>
       </c>
       <c r="C59" t="n">
-        <v>0.6300163940019244</v>
+        <v>0.9060139072299763</v>
       </c>
     </row>
     <row r="60">
@@ -1091,7 +1091,7 @@
         <v>0.8620689655172414</v>
       </c>
       <c r="C60" t="n">
-        <v>0.599890502924929</v>
+        <v>0.889089476830632</v>
       </c>
     </row>
     <row r="61">
@@ -1102,7 +1102,7 @@
         <v>0.8474576271186441</v>
       </c>
       <c r="C61" t="n">
-        <v>0.5712376945757917</v>
+        <v>0.8565377390955971</v>
       </c>
     </row>
     <row r="62">
@@ -1113,7 +1113,7 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="C62" t="n">
-        <v>0.5443741453959811</v>
+        <v>0.8161557479386742</v>
       </c>
     </row>
     <row r="63">
@@ -1124,7 +1124,7 @@
         <v>0.819672131147541</v>
       </c>
       <c r="C63" t="n">
-        <v>0.5220311361463558</v>
+        <v>0.7800468137519276</v>
       </c>
     </row>
     <row r="64">
@@ -1135,7 +1135,7 @@
         <v>0.8064516129032259</v>
       </c>
       <c r="C64" t="n">
-        <v>0.5047598890104078</v>
+        <v>0.7377541088690953</v>
       </c>
     </row>
     <row r="65">
@@ -1146,7 +1146,7 @@
         <v>0.7936507936507936</v>
       </c>
       <c r="C65" t="n">
-        <v>0.488448754335759</v>
+        <v>0.7064941772072812</v>
       </c>
     </row>
     <row r="66">
@@ -1157,7 +1157,7 @@
         <v>0.78125</v>
       </c>
       <c r="C66" t="n">
-        <v>0.4730098935857296</v>
+        <v>0.6740048825237153</v>
       </c>
     </row>
     <row r="67">
@@ -1168,7 +1168,7 @@
         <v>0.7692307692307692</v>
       </c>
       <c r="C67" t="n">
-        <v>0.4582521937248782</v>
+        <v>0.6474113977583942</v>
       </c>
     </row>
     <row r="68">
@@ -1179,7 +1179,7 @@
         <v>0.7575757575757576</v>
       </c>
       <c r="C68" t="n">
-        <v>0.4441140512505594</v>
+        <v>0.6247173064300181</v>
       </c>
     </row>
     <row r="69">
@@ -1190,7 +1190,7 @@
         <v>0.7462686567164178</v>
       </c>
       <c r="C69" t="n">
-        <v>0.4305617950792087</v>
+        <v>0.6003836719903914</v>
       </c>
     </row>
     <row r="70">
@@ -1201,7 +1201,7 @@
         <v>0.7352941176470588</v>
       </c>
       <c r="C70" t="n">
-        <v>0.4177547676127972</v>
+        <v>0.5752581620902161</v>
       </c>
     </row>
     <row r="71">
@@ -1212,7 +1212,7 @@
         <v>0.7246376811594202</v>
       </c>
       <c r="C71" t="n">
-        <v>0.4062486249745059</v>
+        <v>0.5562177848692761</v>
       </c>
     </row>
     <row r="72">
@@ -1223,7 +1223,7 @@
         <v>0.7142857142857142</v>
       </c>
       <c r="C72" t="n">
-        <v>0.3957073413429483</v>
+        <v>0.538731247960762</v>
       </c>
     </row>
     <row r="73">
@@ -1234,7 +1234,7 @@
         <v>0.7042253521126761</v>
       </c>
       <c r="C73" t="n">
-        <v>0.3857910515995905</v>
+        <v>0.5219489685633282</v>
       </c>
     </row>
     <row r="74">
@@ -1245,7 +1245,7 @@
         <v>0.6944444444444444</v>
       </c>
       <c r="C74" t="n">
-        <v>0.3769225679772696</v>
+        <v>0.5058450623758181</v>
       </c>
     </row>
     <row r="75">
@@ -1256,7 +1256,7 @@
         <v>0.684931506849315</v>
       </c>
       <c r="C75" t="n">
-        <v>0.3682555588726389</v>
+        <v>0.4906862799568035</v>
       </c>
     </row>
     <row r="76">
@@ -1267,7 +1267,7 @@
         <v>0.6756756756756757</v>
       </c>
       <c r="C76" t="n">
-        <v>0.3598440049619399</v>
+        <v>0.4779348874527162</v>
       </c>
     </row>
     <row r="77">
@@ -1278,7 +1278,7 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="C77" t="n">
-        <v>0.3516047122650913</v>
+        <v>0.4656952874426128</v>
       </c>
     </row>
     <row r="78">
@@ -1289,7 +1289,7 @@
         <v>0.6578947368421053</v>
       </c>
       <c r="C78" t="n">
-        <v>0.3435993943535134</v>
+        <v>0.4539381035440077</v>
       </c>
     </row>
     <row r="79">
@@ -1300,7 +1300,7 @@
         <v>0.6493506493506493</v>
       </c>
       <c r="C79" t="n">
-        <v>0.3358640356187488</v>
+        <v>0.4426350887389564</v>
       </c>
     </row>
     <row r="80">
@@ -1311,7 +1311,7 @@
         <v>0.641025641025641</v>
       </c>
       <c r="C80" t="n">
-        <v>0.3283963249737318</v>
+        <v>0.4317690880901862</v>
       </c>
     </row>
     <row r="81">
@@ -1322,7 +1322,7 @@
         <v>0.6329113924050632</v>
       </c>
       <c r="C81" t="n">
-        <v>0.3211770635613231</v>
+        <v>0.421306988248102</v>
       </c>
     </row>
     <row r="82">
@@ -1333,7 +1333,7 @@
         <v>0.625</v>
       </c>
       <c r="C82" t="n">
-        <v>0.3141550428845276</v>
+        <v>0.4112209993449211</v>
       </c>
     </row>
     <row r="83">
@@ -1344,7 +1344,7 @@
         <v>0.6172839506172839</v>
       </c>
       <c r="C83" t="n">
-        <v>0.3072823860747896</v>
+        <v>0.4014877409614384</v>
       </c>
     </row>
     <row r="84">
@@ -1355,7 +1355,7 @@
         <v>0.6097560975609756</v>
       </c>
       <c r="C84" t="n">
-        <v>0.3004842008335991</v>
+        <v>0.3920852589780976</v>
       </c>
     </row>
     <row r="85">
@@ -1366,7 +1366,7 @@
         <v>0.6024096385542168</v>
       </c>
       <c r="C85" t="n">
-        <v>0.2937002170028967</v>
+        <v>0.3829931420907001</v>
       </c>
     </row>
     <row r="86">
@@ -1377,7 +1377,7 @@
         <v>0.5952380952380952</v>
       </c>
       <c r="C86" t="n">
-        <v>0.2868486999942525</v>
+        <v>0.3741926359995189</v>
       </c>
     </row>
     <row r="87">
@@ -1388,7 +1388,7 @@
         <v>0.5882352941176471</v>
       </c>
       <c r="C87" t="n">
-        <v>0.2799360479872116</v>
+        <v>0.3656667386055658</v>
       </c>
     </row>
     <row r="88">
@@ -1399,7 +1399,7 @@
         <v>0.5813953488372093</v>
       </c>
       <c r="C88" t="n">
-        <v>0.2728942888156106</v>
+        <v>0.3574002612019169</v>
       </c>
     </row>
     <row r="89">
@@ -1410,7 +1410,7 @@
         <v>0.5747126436781609</v>
       </c>
       <c r="C89" t="n">
-        <v>0.2666339402799603</v>
+        <v>0.349379844471113</v>
       </c>
     </row>
     <row r="90">
@@ -1421,7 +1421,7 @@
         <v>0.5681818181818182</v>
       </c>
       <c r="C90" t="n">
-        <v>0.260363054356204</v>
+        <v>0.3415939232281059</v>
       </c>
     </row>
     <row r="91">
@@ -1432,7 +1432,7 @@
         <v>0.5617977528089888</v>
       </c>
       <c r="C91" t="n">
-        <v>0.2539823145864648</v>
+        <v>0.3354575544404367</v>
       </c>
     </row>
     <row r="92">
@@ -1443,7 +1443,7 @@
         <v>0.5555555555555556</v>
       </c>
       <c r="C92" t="n">
-        <v>0.2484231414099346</v>
+        <v>0.3295182369241912</v>
       </c>
     </row>
     <row r="93">
@@ -1454,7 +1454,7 @@
         <v>0.5494505494505494</v>
       </c>
       <c r="C93" t="n">
-        <v>0.2435923551591467</v>
+        <v>0.3236046209688352</v>
       </c>
     </row>
     <row r="94">
@@ -1465,7 +1465,7 @@
         <v>0.5434782608695652</v>
       </c>
       <c r="C94" t="n">
-        <v>0.2388105267852642</v>
+        <v>0.3176843977824559</v>
       </c>
     </row>
     <row r="95">
@@ -1476,7 +1476,7 @@
         <v>0.5376344086021505</v>
       </c>
       <c r="C95" t="n">
-        <v>0.233829149164625</v>
+        <v>0.3117290507344435</v>
       </c>
     </row>
     <row r="96">
@@ -1487,7 +1487,7 @@
         <v>0.5319148936170213</v>
       </c>
       <c r="C96" t="n">
-        <v>0.2286756749839349</v>
+        <v>0.3057162021751379</v>
       </c>
     </row>
     <row r="97">
@@ -1498,7 +1498,7 @@
         <v>0.5263157894736842</v>
       </c>
       <c r="C97" t="n">
-        <v>0.2233688557815822</v>
+        <v>0.2996311661986636</v>
       </c>
     </row>
     <row r="98">
@@ -1509,7 +1509,7 @@
         <v>0.5208333333333334</v>
       </c>
       <c r="C98" t="n">
-        <v>0.2179637535571073</v>
+        <v>0.2934677048436283</v>
       </c>
     </row>
     <row r="99">
@@ -1520,7 +1520,7 @@
         <v>0.5154639175257733</v>
       </c>
       <c r="C99" t="n">
-        <v>0.2129231126203859</v>
+        <v>0.2872280559748516</v>
       </c>
     </row>
     <row r="100">
@@ -1531,7 +1531,7 @@
         <v>0.5102040816326531</v>
       </c>
       <c r="C100" t="n">
-        <v>0.2081457651315101</v>
+        <v>0.2809223497294466</v>
       </c>
     </row>
     <row r="101">
@@ -1542,7 +1542,7 @@
         <v>0.5050505050505051</v>
       </c>
       <c r="C101" t="n">
-        <v>0.2037808647284532</v>
+        <v>0.2745675577065596</v>
       </c>
     </row>
     <row r="102">
@@ -1553,7 +1553,7 @@
         <v>0.5</v>
       </c>
       <c r="C102" t="n">
-        <v>0.1994523782479159</v>
+        <v>0.2681861277522768</v>
       </c>
     </row>
     <row r="103">
@@ -1564,7 +1564,7 @@
         <v>0.495049504950495</v>
       </c>
       <c r="C103" t="n">
-        <v>0.1951704424566346</v>
+        <v>0.2618130428874326</v>
       </c>
     </row>
     <row r="104">
@@ -1575,7 +1575,7 @@
         <v>0.4901960784313725</v>
       </c>
       <c r="C104" t="n">
-        <v>0.1909597328055463</v>
+        <v>0.2554694725977629</v>
       </c>
     </row>
     <row r="105">
@@ -1586,7 +1586,7 @@
         <v>0.4854368932038835</v>
       </c>
       <c r="C105" t="n">
-        <v>0.1868174725788629</v>
+        <v>0.2491825441951814</v>
       </c>
     </row>
     <row r="106">
@@ -1597,7 +1597,7 @@
         <v>0.4807692307692307</v>
       </c>
       <c r="C106" t="n">
-        <v>0.1827598291622584</v>
+        <v>0.2440814898509022</v>
       </c>
     </row>
     <row r="107">
@@ -1608,7 +1608,7 @@
         <v>0.4761904761904762</v>
       </c>
       <c r="C107" t="n">
-        <v>0.1788219073334709</v>
+        <v>0.2408258848216604</v>
       </c>
     </row>
     <row r="108">
@@ -1619,7 +1619,7 @@
         <v>0.4716981132075471</v>
       </c>
       <c r="C108" t="n">
-        <v>0.1752117999992869</v>
+        <v>0.238050465859597</v>
       </c>
     </row>
     <row r="109">
@@ -1630,7 +1630,7 @@
         <v>0.4672897196261682</v>
       </c>
       <c r="C109" t="n">
-        <v>0.1722049687809217</v>
+        <v>0.2352305343661629</v>
       </c>
     </row>
     <row r="110">
@@ -1641,7 +1641,7 @@
         <v>0.4629629629629629</v>
       </c>
       <c r="C110" t="n">
-        <v>0.1692556922490758</v>
+        <v>0.2323553954695444</v>
       </c>
     </row>
     <row r="111">
@@ -1652,7 +1652,7 @@
         <v>0.4587155963302752</v>
       </c>
       <c r="C111" t="n">
-        <v>0.1663627275397943</v>
+        <v>0.2294206225240106</v>
       </c>
     </row>
     <row r="112">
@@ -1663,7 +1663,7 @@
         <v>0.4545454545454545</v>
       </c>
       <c r="C112" t="n">
-        <v>0.1635269979728668</v>
+        <v>0.2264270394367913</v>
       </c>
     </row>
     <row r="113">
@@ -1674,7 +1674,7 @@
         <v>0.4504504504504504</v>
       </c>
       <c r="C113" t="n">
-        <v>0.1607445539834969</v>
+        <v>0.2233801975286696</v>
       </c>
     </row>
     <row r="114">
@@ -1685,7 +1685,7 @@
         <v>0.4464285714285714</v>
       </c>
       <c r="C114" t="n">
-        <v>0.1582652410985019</v>
+        <v>0.2202776598726474</v>
       </c>
     </row>
     <row r="115">
@@ -1696,7 +1696,7 @@
         <v>0.4424778761061947</v>
       </c>
       <c r="C115" t="n">
-        <v>0.1558605970338312</v>
+        <v>0.2171255718653057</v>
       </c>
     </row>
     <row r="116">
@@ -1707,7 +1707,7 @@
         <v>0.4385964912280702</v>
       </c>
       <c r="C116" t="n">
-        <v>0.1535027535770318</v>
+        <v>0.2139418834185264</v>
       </c>
     </row>
     <row r="117">
@@ -1718,7 +1718,7 @@
         <v>0.4347826086956521</v>
       </c>
       <c r="C117" t="n">
-        <v>0.15118835410168</v>
+        <v>0.2107221130204365</v>
       </c>
     </row>
     <row r="118">
@@ -1729,7 +1729,7 @@
         <v>0.4310344827586207</v>
       </c>
       <c r="C118" t="n">
-        <v>0.1489142083247394</v>
+        <v>0.2074744821320522</v>
       </c>
     </row>
     <row r="119">
@@ -1740,7 +1740,7 @@
         <v>0.4273504273504274</v>
       </c>
       <c r="C119" t="n">
-        <v>0.1466773404329423</v>
+        <v>0.2042074428787813</v>
       </c>
     </row>
     <row r="120">
@@ -1751,7 +1751,7 @@
         <v>0.4237288135593221</v>
       </c>
       <c r="C120" t="n">
-        <v>0.1444750257303262</v>
+        <v>0.200929411751521</v>
       </c>
     </row>
     <row r="121">
@@ -1762,7 +1762,7 @@
         <v>0.4201680672268908</v>
       </c>
       <c r="C121" t="n">
-        <v>0.1423048163358011</v>
+        <v>0.19764855702591</v>
       </c>
     </row>
     <row r="122">
@@ -1773,7 +1773,7 @@
         <v>0.4166666666666667</v>
       </c>
       <c r="C122" t="n">
-        <v>0.1401645568157199</v>
+        <v>0.1943726367040498</v>
       </c>
     </row>
     <row r="123">
@@ -1784,7 +1784,7 @@
         <v>0.4132231404958678</v>
       </c>
       <c r="C123" t="n">
-        <v>0.1380523907790873</v>
+        <v>0.191108882288917</v>
       </c>
     </row>
     <row r="124">
@@ -1795,7 +1795,7 @@
         <v>0.4098360655737705</v>
       </c>
       <c r="C124" t="n">
-        <v>0.1359667595986543</v>
+        <v>0.1878639228652063</v>
       </c>
     </row>
     <row r="125">
@@ -1806,7 +1806,7 @@
         <v>0.4065040650406504</v>
       </c>
       <c r="C125" t="n">
-        <v>0.133906394448163</v>
+        <v>0.1846437434999004</v>
       </c>
     </row>
     <row r="126">
@@ -1817,7 +1817,7 @@
         <v>0.4032258064516129</v>
       </c>
       <c r="C126" t="n">
-        <v>0.1318703028606193</v>
+        <v>0.1814536719644522</v>
       </c>
     </row>
     <row r="127">
@@ -1828,7 +1828,7 @@
         <v>0.4</v>
       </c>
       <c r="C127" t="n">
-        <v>0.1298577509429833</v>
+        <v>0.1783023663386534</v>
       </c>
     </row>
     <row r="128">
@@ -1839,7 +1839,7 @@
         <v>0.3968253968253968</v>
       </c>
       <c r="C128" t="n">
-        <v>0.127868242335915</v>
+        <v>0.1751891813537757</v>
       </c>
     </row>
     <row r="129">
@@ -1850,7 +1850,7 @@
         <v>0.3937007874015748</v>
       </c>
       <c r="C129" t="n">
-        <v>0.1259014948923251</v>
+        <v>0.1721175984141954</v>
       </c>
     </row>
     <row r="130">
@@ -1861,7 +1861,7 @@
         <v>0.390625</v>
       </c>
       <c r="C130" t="n">
-        <v>0.1239574159489016</v>
+        <v>0.1690906079568013</v>
       </c>
     </row>
     <row r="131">
@@ -1872,7 +1872,7 @@
         <v>0.3875968992248062</v>
       </c>
       <c r="C131" t="n">
-        <v>0.1220360769573922</v>
+        <v>0.1661107144642788</v>
       </c>
     </row>
     <row r="132">
@@ -1883,7 +1883,7 @@
         <v>0.3846153846153846</v>
       </c>
       <c r="C132" t="n">
-        <v>0.1201376881295523</v>
+        <v>0.1631800027962835</v>
       </c>
     </row>
     <row r="133">
@@ -1894,7 +1894,7 @@
         <v>0.3816793893129771</v>
       </c>
       <c r="C133" t="n">
-        <v>0.1182632335955778</v>
+        <v>0.1603008342743404</v>
       </c>
     </row>
     <row r="134">
@@ -1905,7 +1905,7 @@
         <v>0.3787878787878788</v>
       </c>
       <c r="C134" t="n">
-        <v>0.116413249010805</v>
+        <v>0.1574738988002561</v>
       </c>
     </row>
     <row r="135">
@@ -1916,7 +1916,7 @@
         <v>0.3759398496240601</v>
       </c>
       <c r="C135" t="n">
-        <v>0.1145874040002402</v>
+        <v>0.154700269065503</v>
       </c>
     </row>
     <row r="136">
@@ -1927,7 +1927,7 @@
         <v>0.3731343283582089</v>
       </c>
       <c r="C136" t="n">
-        <v>0.1127862277857479</v>
+        <v>0.1519807739203538</v>
       </c>
     </row>
     <row r="137">
@@ -1938,7 +1938,7 @@
         <v>0.3703703703703703</v>
       </c>
       <c r="C137" t="n">
-        <v>0.1110296687645092</v>
+        <v>0.1493160356341941</v>
       </c>
     </row>
     <row r="138">
@@ -1949,7 +1949,7 @@
         <v>0.3676470588235294</v>
       </c>
       <c r="C138" t="n">
-        <v>0.109644475714052</v>
+        <v>0.1467124932198392</v>
       </c>
     </row>
     <row r="139">
@@ -1960,7 +1960,7 @@
         <v>0.364963503649635</v>
       </c>
       <c r="C139" t="n">
-        <v>0.1081965193463174</v>
+        <v>0.1441643977653418</v>
       </c>
     </row>
     <row r="140">
@@ -1971,7 +1971,7 @@
         <v>0.3623188405797101</v>
       </c>
       <c r="C140" t="n">
-        <v>0.106678062290122</v>
+        <v>0.1416718343406093</v>
       </c>
     </row>
     <row r="141">
@@ -1982,7 +1982,7 @@
         <v>0.3597122302158273</v>
       </c>
       <c r="C141" t="n">
-        <v>0.1055406720452814</v>
+        <v>0.1392348793034633</v>
       </c>
     </row>
     <row r="142">
@@ -1993,7 +1993,7 @@
         <v>0.3571428571428571</v>
       </c>
       <c r="C142" t="n">
-        <v>0.1044610046290322</v>
+        <v>0.1370568659420044</v>
       </c>
     </row>
     <row r="143">
@@ -2004,7 +2004,7 @@
         <v>0.3546099290780142</v>
       </c>
       <c r="C143" t="n">
-        <v>0.1033179944862136</v>
+        <v>0.1351236872314516</v>
       </c>
     </row>
     <row r="144">
@@ -2015,7 +2015,7 @@
         <v>0.3521126760563381</v>
       </c>
       <c r="C144" t="n">
-        <v>0.102097562314969</v>
+        <v>0.1332278701221142</v>
       </c>
     </row>
     <row r="145">
@@ -2026,7 +2026,7 @@
         <v>0.3496503496503497</v>
       </c>
       <c r="C145" t="n">
-        <v>0.1007972251017134</v>
+        <v>0.1313688423595479</v>
       </c>
     </row>
     <row r="146">
@@ -2037,7 +2037,7 @@
         <v>0.3472222222222222</v>
       </c>
       <c r="C146" t="n">
-        <v>0.09942860356042886</v>
+        <v>0.1295487861330799</v>
       </c>
     </row>
     <row r="147">
@@ -2048,7 +2048,7 @@
         <v>0.3448275862068966</v>
       </c>
       <c r="C147" t="n">
-        <v>0.09808665569421468</v>
+        <v>0.1277663791500516</v>
       </c>
     </row>
     <row r="148">
@@ -2059,7 +2059,7 @@
         <v>0.3424657534246575</v>
       </c>
       <c r="C148" t="n">
-        <v>0.09692340623827432</v>
+        <v>0.1260210317984343</v>
       </c>
     </row>
     <row r="149">
@@ -2070,7 +2070,7 @@
         <v>0.3401360544217687</v>
       </c>
       <c r="C149" t="n">
-        <v>0.09574055272043196</v>
+        <v>0.1243128668394189</v>
       </c>
     </row>
     <row r="150">
@@ -2081,7 +2081,7 @@
         <v>0.3378378378378378</v>
       </c>
       <c r="C150" t="n">
-        <v>0.09453722392001827</v>
+        <v>0.1226384395380234</v>
       </c>
     </row>
     <row r="151">
@@ -2092,7 +2092,7 @@
         <v>0.3355704697986577</v>
       </c>
       <c r="C151" t="n">
-        <v>0.09331588490345062</v>
+        <v>0.1209971757264594</v>
       </c>
     </row>
     <row r="152">
@@ -2103,7 +2103,7 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="C152" t="n">
-        <v>0.09208131738692649</v>
+        <v>0.1193884958566753</v>
       </c>
     </row>
     <row r="153">
@@ -2114,7 +2114,7 @@
         <v>0.3311258278145696</v>
       </c>
       <c r="C153" t="n">
-        <v>0.09083838387936648</v>
+        <v>0.1178118149081866</v>
       </c>
     </row>
     <row r="154">
@@ -2125,7 +2125,7 @@
         <v>0.3289473684210527</v>
       </c>
       <c r="C154" t="n">
-        <v>0.08959023917843505</v>
+        <v>0.1162665426089842</v>
       </c>
     </row>
     <row r="155">
@@ -2136,7 +2136,7 @@
         <v>0.326797385620915</v>
       </c>
       <c r="C155" t="n">
-        <v>0.08833614536745282</v>
+        <v>0.1147520838870105</v>
       </c>
     </row>
     <row r="156">
@@ -2147,7 +2147,7 @@
         <v>0.3246753246753247</v>
       </c>
       <c r="C156" t="n">
-        <v>0.08707946258117298</v>
+        <v>0.1132678395450239</v>
       </c>
     </row>
     <row r="157">
@@ -2158,7 +2158,7 @@
         <v>0.3225806451612903</v>
       </c>
       <c r="C157" t="n">
-        <v>0.08582350792270468</v>
+        <v>0.111813207063936</v>
       </c>
     </row>
     <row r="158">
@@ -2169,7 +2169,7 @@
         <v>0.3205128205128205</v>
       </c>
       <c r="C158" t="n">
-        <v>0.08457365544149673</v>
+        <v>0.1103875815469547</v>
       </c>
     </row>
     <row r="159">
@@ -2180,7 +2180,7 @@
         <v>0.3184713375796178</v>
       </c>
       <c r="C159" t="n">
-        <v>0.08361885720821981</v>
+        <v>0.1089903567229595</v>
       </c>
     </row>
     <row r="160">
@@ -2191,7 +2191,7 @@
         <v>0.3164556962025316</v>
       </c>
       <c r="C160" t="n">
-        <v>0.08266093181574016</v>
+        <v>0.1076209260196788</v>
       </c>
     </row>
     <row r="161">
@@ -2202,7 +2202,7 @@
         <v>0.3144654088050314</v>
       </c>
       <c r="C161" t="n">
-        <v>0.08168042125695821</v>
+        <v>0.1062786836399266</v>
       </c>
     </row>
     <row r="162">
@@ -2213,7 +2213,7 @@
         <v>0.3125</v>
       </c>
       <c r="C162" t="n">
-        <v>0.08068091127742209</v>
+        <v>0.1049630256613523</v>
       </c>
     </row>
     <row r="163">
@@ -2224,7 +2224,7 @@
         <v>0.3105590062111801</v>
       </c>
       <c r="C163" t="n">
-        <v>0.0796660999612562</v>
+        <v>0.1036733511022629</v>
       </c>
     </row>
     <row r="164">
@@ -2235,7 +2235,7 @@
         <v>0.308641975308642</v>
       </c>
       <c r="C164" t="n">
-        <v>0.07863977113466911</v>
+        <v>0.1024090629686595</v>
       </c>
     </row>
     <row r="165">
@@ -2246,7 +2246,7 @@
         <v>0.3067484662576687</v>
       </c>
       <c r="C165" t="n">
-        <v>0.07760900530176011</v>
+        <v>0.1011695692484961</v>
       </c>
     </row>
     <row r="166">
@@ -2257,7 +2257,7 @@
         <v>0.3048780487804878</v>
       </c>
       <c r="C166" t="n">
-        <v>0.07657356309897242</v>
+        <v>0.09995428385458184</v>
       </c>
     </row>
     <row r="167">
@@ -2268,7 +2268,7 @@
         <v>0.303030303030303</v>
       </c>
       <c r="C167" t="n">
-        <v>0.07568654514175942</v>
+        <v>0.09876262750935726</v>
       </c>
     </row>
     <row r="168">
@@ -2279,7 +2279,7 @@
         <v>0.3012048192771084</v>
       </c>
       <c r="C168" t="n">
-        <v>0.07480744557394932</v>
+        <v>0.09759402855886891</v>
       </c>
     </row>
     <row r="169">
@@ -2290,7 +2290,7 @@
         <v>0.2994011976047904</v>
       </c>
       <c r="C169" t="n">
-        <v>0.07392851134146984</v>
+        <v>0.09644808939183536</v>
       </c>
     </row>
     <row r="170">
@@ -2301,7 +2301,7 @@
         <v>0.2976190476190476</v>
       </c>
       <c r="C170" t="n">
-        <v>0.07305339393687152</v>
+        <v>0.09532787419545247</v>
       </c>
     </row>
     <row r="171">
@@ -2312,7 +2312,7 @@
         <v>0.2958579881656805</v>
       </c>
       <c r="C171" t="n">
-        <v>0.07218164011221968</v>
+        <v>0.09423093821597642</v>
       </c>
     </row>
     <row r="172">
@@ -2323,7 +2323,7 @@
         <v>0.2941176470588235</v>
       </c>
       <c r="C172" t="n">
-        <v>0.07133591890131052</v>
+        <v>0.09315665938565455</v>
       </c>
     </row>
     <row r="173">
@@ -2334,7 +2334,7 @@
         <v>0.2923976608187134</v>
       </c>
       <c r="C173" t="n">
-        <v>0.07055173821010322</v>
+        <v>0.09210254703793207</v>
       </c>
     </row>
     <row r="174">
@@ -2345,7 +2345,7 @@
         <v>0.2906976744186047</v>
       </c>
       <c r="C174" t="n">
-        <v>0.06977256238698004</v>
+        <v>0.09106809258197339</v>
       </c>
     </row>
     <row r="175">
@@ -2356,7 +2356,7 @@
         <v>0.2890173410404624</v>
       </c>
       <c r="C175" t="n">
-        <v>0.06900682624636252</v>
+        <v>0.09005279861670638</v>
       </c>
     </row>
     <row r="176">
@@ -2367,7 +2367,7 @@
         <v>0.2873563218390804</v>
       </c>
       <c r="C176" t="n">
-        <v>0.06830705784960493</v>
+        <v>0.08905617919120211</v>
       </c>
     </row>
     <row r="177">
@@ -2378,7 +2378,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="C177" t="n">
-        <v>0.06761424652964712</v>
+        <v>0.08807776000391962</v>
       </c>
     </row>
     <row r="178">
@@ -2389,7 +2389,7 @@
         <v>0.2840909090909091</v>
       </c>
       <c r="C178" t="n">
-        <v>0.06692876789991536</v>
+        <v>0.08711707854902649</v>
       </c>
     </row>
     <row r="179">
@@ -2400,7 +2400,7 @@
         <v>0.2824858757062147</v>
       </c>
       <c r="C179" t="n">
-        <v>0.06625095407456022</v>
+        <v>0.08617368420014067</v>
       </c>
     </row>
     <row r="180">
@@ -2411,7 +2411,7 @@
         <v>0.2808988764044944</v>
       </c>
       <c r="C180" t="n">
-        <v>0.0655810943061403</v>
+        <v>0.08524713825846826</v>
       </c>
     </row>
     <row r="181">
@@ -2422,7 +2422,7 @@
         <v>0.2793296089385475</v>
       </c>
       <c r="C181" t="n">
-        <v>0.06492113540179939</v>
+        <v>0.08433871334427279</v>
       </c>
     </row>
     <row r="182">
@@ -2433,7 +2433,7 @@
         <v>0.2777777777777778</v>
       </c>
       <c r="C182" t="n">
-        <v>0.06427085105299293</v>
+        <v>0.08344756133881601</v>
       </c>
     </row>
     <row r="183">
@@ -2444,7 +2444,7 @@
         <v>0.2762430939226519</v>
       </c>
       <c r="C183" t="n">
-        <v>0.06362907538329887</v>
+        <v>0.08257194523506638</v>
       </c>
     </row>
     <row r="184">
@@ -2455,7 +2455,7 @@
         <v>0.2747252747252747</v>
       </c>
       <c r="C184" t="n">
-        <v>0.06299594113166986</v>
+        <v>0.0817114753784277</v>
       </c>
     </row>
     <row r="185">
@@ -2466,7 +2466,7 @@
         <v>0.273224043715847</v>
       </c>
       <c r="C185" t="n">
-        <v>0.06237154592880156</v>
+        <v>0.08086577359642985</v>
       </c>
     </row>
     <row r="186">
@@ -2477,7 +2477,7 @@
         <v>0.2717391304347826</v>
       </c>
       <c r="C186" t="n">
-        <v>0.0617559544242881</v>
+        <v>0.08003447302744843</v>
       </c>
     </row>
     <row r="187">
@@ -2488,7 +2488,7 @@
         <v>0.2702702702702702</v>
       </c>
       <c r="C187" t="n">
-        <v>0.06114920049897857</v>
+        <v>0.07921721792550712</v>
       </c>
     </row>
     <row r="188">
@@ -2499,7 +2499,7 @@
         <v>0.2688172043010753</v>
       </c>
       <c r="C188" t="n">
-        <v>0.06055219970168047</v>
+        <v>0.07841366344596663</v>
       </c>
     </row>
     <row r="189">
@@ -2510,7 +2510,7 @@
         <v>0.267379679144385</v>
       </c>
       <c r="C189" t="n">
-        <v>0.05998290091107172</v>
+        <v>0.07762347540730825</v>
       </c>
     </row>
     <row r="190">
@@ -2521,7 +2521,7 @@
         <v>0.2659574468085106</v>
       </c>
       <c r="C190" t="n">
-        <v>0.05942195484047339</v>
+        <v>0.07684633005292012</v>
       </c>
     </row>
     <row r="191">
@@ -2532,7 +2532,7 @@
         <v>0.2645502645502645</v>
       </c>
       <c r="C191" t="n">
-        <v>0.0588692497429374</v>
+        <v>0.07608191378761928</v>
       </c>
     </row>
     <row r="192">
@@ -2543,7 +2543,7 @@
         <v>0.2631578947368421</v>
       </c>
       <c r="C192" t="n">
-        <v>0.05832467297804519</v>
+        <v>0.07532992291347211</v>
       </c>
     </row>
     <row r="193">
@@ -2554,7 +2554,7 @@
         <v>0.2617801047120419</v>
       </c>
       <c r="C193" t="n">
-        <v>0.05778811118553442</v>
+        <v>0.07459006335454985</v>
       </c>
     </row>
     <row r="194">
@@ -2565,7 +2565,7 @@
         <v>0.2604166666666667</v>
       </c>
       <c r="C194" t="n">
-        <v>0.05725945045075741</v>
+        <v>0.07386205038004716</v>
       </c>
     </row>
     <row r="195">
@@ -2576,7 +2576,7 @@
         <v>0.2590673575129534</v>
       </c>
       <c r="C195" t="n">
-        <v>0.05673857646160876</v>
+        <v>0.07314560832424873</v>
       </c>
     </row>
     <row r="196">
@@ -2587,7 +2587,7 @@
         <v>0.2577319587628866</v>
       </c>
       <c r="C196" t="n">
-        <v>0.05622537465032558</v>
+        <v>0.07244047029689496</v>
       </c>
     </row>
     <row r="197">
@@ -2598,7 +2598,7 @@
         <v>0.2564102564102564</v>
       </c>
       <c r="C197" t="n">
-        <v>0.05571973033755419</v>
+        <v>0.07174637790766196</v>
       </c>
     </row>
     <row r="198">
@@ -2609,7 +2609,7 @@
         <v>0.2551020408163265</v>
       </c>
       <c r="C198" t="n">
-        <v>0.05522231623174437</v>
+        <v>0.07106386835223157</v>
       </c>
     </row>
     <row r="199">
@@ -2620,7 +2620,7 @@
         <v>0.2538071065989848</v>
       </c>
       <c r="C199" t="n">
-        <v>0.05473389461395585</v>
+        <v>0.07050778002613667</v>
       </c>
     </row>
     <row r="200">
@@ -2631,7 +2631,7 @@
         <v>0.2525252525252525</v>
       </c>
       <c r="C200" t="n">
-        <v>0.05425264032072735</v>
+        <v>0.07000318993204671</v>
       </c>
     </row>
     <row r="201">
@@ -2642,7 +2642,7 @@
         <v>0.2512562814070352</v>
       </c>
       <c r="C201" t="n">
-        <v>0.05377844043252767</v>
+        <v>0.06950584870609218</v>
       </c>
     </row>
     <row r="202">
@@ -2653,7 +2653,7 @@
         <v>0.25</v>
       </c>
       <c r="C202" t="n">
-        <v>0.05331118246351823</v>
+        <v>0.06901540673923164</v>
       </c>
     </row>
   </sheetData>

--- a/Python for Project Work SRE_Part 2/ERS/ERS/ERS_Means/SA_el_hor1_mean.xlsx
+++ b/Python for Project Work SRE_Part 2/ERS/ERS/ERS_Means/SA_el_hor1_mean.xlsx
@@ -464,7 +464,7 @@
         <v>50</v>
       </c>
       <c r="C3" t="n">
-        <v>5.149764880902457</v>
+        <v>5.209775404733045</v>
       </c>
     </row>
     <row r="4">
@@ -475,7 +475,7 @@
         <v>25</v>
       </c>
       <c r="C4" t="n">
-        <v>5.480278356573172</v>
+        <v>5.807330645985359</v>
       </c>
     </row>
     <row r="5">
@@ -486,7 +486,7 @@
         <v>16.66666666666667</v>
       </c>
       <c r="C5" t="n">
-        <v>6.30353963901543</v>
+        <v>8.076801445082753</v>
       </c>
     </row>
     <row r="6">
@@ -497,7 +497,7 @@
         <v>12.5</v>
       </c>
       <c r="C6" t="n">
-        <v>7.572250483386243</v>
+        <v>10.06419748652128</v>
       </c>
     </row>
     <row r="7">
@@ -508,7 +508,7 @@
         <v>10</v>
       </c>
       <c r="C7" t="n">
-        <v>8.739743924642159</v>
+        <v>11.60473713523046</v>
       </c>
     </row>
     <row r="8">
@@ -519,7 +519,7 @@
         <v>8.333333333333334</v>
       </c>
       <c r="C8" t="n">
-        <v>10.74926585713837</v>
+        <v>10.74828953504452</v>
       </c>
     </row>
     <row r="9">
@@ -530,7 +530,7 @@
         <v>7.142857142857142</v>
       </c>
       <c r="C9" t="n">
-        <v>11.67012151851182</v>
+        <v>11.50210995319536</v>
       </c>
     </row>
     <row r="10">
@@ -541,7 +541,7 @@
         <v>6.25</v>
       </c>
       <c r="C10" t="n">
-        <v>11.52624685708802</v>
+        <v>10.02811736247793</v>
       </c>
     </row>
     <row r="11">
@@ -552,7 +552,7 @@
         <v>5.555555555555555</v>
       </c>
       <c r="C11" t="n">
-        <v>12.71231452894861</v>
+        <v>9.951019208968212</v>
       </c>
     </row>
     <row r="12">
@@ -563,7 +563,7 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>12.22939888769194</v>
+        <v>9.902683471929398</v>
       </c>
     </row>
     <row r="13">
@@ -574,7 +574,7 @@
         <v>4.545454545454546</v>
       </c>
       <c r="C13" t="n">
-        <v>11.76302350518593</v>
+        <v>9.855155629377238</v>
       </c>
     </row>
     <row r="14">
@@ -585,7 +585,7 @@
         <v>4.166666666666667</v>
       </c>
       <c r="C14" t="n">
-        <v>12.67366601453373</v>
+        <v>9.625604802400199</v>
       </c>
     </row>
     <row r="15">
@@ -596,7 +596,7 @@
         <v>3.846153846153846</v>
       </c>
       <c r="C15" t="n">
-        <v>12.64076174942862</v>
+        <v>9.685251316158149</v>
       </c>
     </row>
     <row r="16">
@@ -607,7 +607,7 @@
         <v>3.571428571428571</v>
       </c>
       <c r="C16" t="n">
-        <v>11.75980427234178</v>
+        <v>9.684611056147915</v>
       </c>
     </row>
     <row r="17">
@@ -618,7 +618,7 @@
         <v>3.333333333333333</v>
       </c>
       <c r="C17" t="n">
-        <v>11.35932473255418</v>
+        <v>9.534304407178576</v>
       </c>
     </row>
     <row r="18">
@@ -629,7 +629,7 @@
         <v>3.125</v>
       </c>
       <c r="C18" t="n">
-        <v>11.16384655628082</v>
+        <v>8.975236787779179</v>
       </c>
     </row>
     <row r="19">
@@ -640,7 +640,7 @@
         <v>2.941176470588235</v>
       </c>
       <c r="C19" t="n">
-        <v>10.6572630691823</v>
+        <v>8.370087552133359</v>
       </c>
     </row>
     <row r="20">
@@ -651,7 +651,7 @@
         <v>2.777777777777778</v>
       </c>
       <c r="C20" t="n">
-        <v>10.27899352009469</v>
+        <v>8.049239269675491</v>
       </c>
     </row>
     <row r="21">
@@ -662,7 +662,7 @@
         <v>2.631578947368421</v>
       </c>
       <c r="C21" t="n">
-        <v>9.955218872679737</v>
+        <v>7.803353391312526</v>
       </c>
     </row>
     <row r="22">
@@ -673,7 +673,7 @@
         <v>2.5</v>
       </c>
       <c r="C22" t="n">
-        <v>9.854550289889035</v>
+        <v>7.370142035072652</v>
       </c>
     </row>
     <row r="23">
@@ -684,7 +684,7 @@
         <v>2.380952380952381</v>
       </c>
       <c r="C23" t="n">
-        <v>9.382039721357918</v>
+        <v>6.832512306022912</v>
       </c>
     </row>
     <row r="24">
@@ -695,7 +695,7 @@
         <v>2.272727272727273</v>
       </c>
       <c r="C24" t="n">
-        <v>9.412850336030745</v>
+        <v>6.161080955427107</v>
       </c>
     </row>
     <row r="25">
@@ -706,7 +706,7 @@
         <v>2.173913043478261</v>
       </c>
       <c r="C25" t="n">
-        <v>9.252892988423248</v>
+        <v>5.651819307706812</v>
       </c>
     </row>
     <row r="26">
@@ -717,7 +717,7 @@
         <v>2.083333333333333</v>
       </c>
       <c r="C26" t="n">
-        <v>8.305040963417381</v>
+        <v>5.175067063878051</v>
       </c>
     </row>
     <row r="27">
@@ -728,7 +728,7 @@
         <v>2</v>
       </c>
       <c r="C27" t="n">
-        <v>7.481876198553166</v>
+        <v>4.789925082894959</v>
       </c>
     </row>
     <row r="28">
@@ -739,7 +739,7 @@
         <v>1.923076923076923</v>
       </c>
       <c r="C28" t="n">
-        <v>6.865773066183914</v>
+        <v>4.484438047811919</v>
       </c>
     </row>
     <row r="29">
@@ -750,7 +750,7 @@
         <v>1.851851851851852</v>
       </c>
       <c r="C29" t="n">
-        <v>6.059656843608845</v>
+        <v>4.224606916782013</v>
       </c>
     </row>
     <row r="30">
@@ -761,7 +761,7 @@
         <v>1.785714285714286</v>
       </c>
       <c r="C30" t="n">
-        <v>5.305121598032979</v>
+        <v>3.99079120723384</v>
       </c>
     </row>
     <row r="31">
@@ -772,7 +772,7 @@
         <v>1.724137931034483</v>
       </c>
       <c r="C31" t="n">
-        <v>4.700416587775391</v>
+        <v>3.608471440850066</v>
       </c>
     </row>
     <row r="32">
@@ -783,7 +783,7 @@
         <v>1.666666666666667</v>
       </c>
       <c r="C32" t="n">
-        <v>4.207997827626266</v>
+        <v>3.200618076411073</v>
       </c>
     </row>
     <row r="33">
@@ -794,7 +794,7 @@
         <v>1.612903225806452</v>
       </c>
       <c r="C33" t="n">
-        <v>3.839312872949</v>
+        <v>2.931565946113395</v>
       </c>
     </row>
     <row r="34">
@@ -805,7 +805,7 @@
         <v>1.5625</v>
       </c>
       <c r="C34" t="n">
-        <v>3.536666768140282</v>
+        <v>2.730021382237624</v>
       </c>
     </row>
     <row r="35">
@@ -816,7 +816,7 @@
         <v>1.515151515151515</v>
       </c>
       <c r="C35" t="n">
-        <v>3.213274111439399</v>
+        <v>2.465818587567659</v>
       </c>
     </row>
     <row r="36">
@@ -827,7 +827,7 @@
         <v>1.470588235294118</v>
       </c>
       <c r="C36" t="n">
-        <v>2.952020597772227</v>
+        <v>2.270367218394923</v>
       </c>
     </row>
     <row r="37">
@@ -838,7 +838,7 @@
         <v>1.428571428571428</v>
       </c>
       <c r="C37" t="n">
-        <v>2.759451393610161</v>
+        <v>2.144876002492675</v>
       </c>
     </row>
     <row r="38">
@@ -849,7 +849,7 @@
         <v>1.388888888888889</v>
       </c>
       <c r="C38" t="n">
-        <v>2.689434164739204</v>
+        <v>2.144837832403341</v>
       </c>
     </row>
     <row r="39">
@@ -860,7 +860,7 @@
         <v>1.351351351351351</v>
       </c>
       <c r="C39" t="n">
-        <v>2.657882859701669</v>
+        <v>2.156296204375916</v>
       </c>
     </row>
     <row r="40">
@@ -871,7 +871,7 @@
         <v>1.315789473684211</v>
       </c>
       <c r="C40" t="n">
-        <v>2.572008329932573</v>
+        <v>2.098666410110609</v>
       </c>
     </row>
     <row r="41">
@@ -882,7 +882,7 @@
         <v>1.282051282051282</v>
       </c>
       <c r="C41" t="n">
-        <v>2.398711183731234</v>
+        <v>1.941819518248851</v>
       </c>
     </row>
     <row r="42">
@@ -893,7 +893,7 @@
         <v>1.25</v>
       </c>
       <c r="C42" t="n">
-        <v>2.135956343085045</v>
+        <v>1.713549881140697</v>
       </c>
     </row>
     <row r="43">
@@ -904,7 +904,7 @@
         <v>1.219512195121951</v>
       </c>
       <c r="C43" t="n">
-        <v>1.957334103593813</v>
+        <v>1.530746175312632</v>
       </c>
     </row>
     <row r="44">
@@ -915,7 +915,7 @@
         <v>1.19047619047619</v>
       </c>
       <c r="C44" t="n">
-        <v>1.837520847293675</v>
+        <v>1.422758683803221</v>
       </c>
     </row>
     <row r="45">
@@ -926,7 +926,7 @@
         <v>1.162790697674419</v>
       </c>
       <c r="C45" t="n">
-        <v>1.733737274204429</v>
+        <v>1.339398831839642</v>
       </c>
     </row>
     <row r="46">
@@ -937,7 +937,7 @@
         <v>1.136363636363636</v>
       </c>
       <c r="C46" t="n">
-        <v>1.637896245435789</v>
+        <v>1.270597069784815</v>
       </c>
     </row>
     <row r="47">
@@ -948,7 +948,7 @@
         <v>1.111111111111111</v>
       </c>
       <c r="C47" t="n">
-        <v>1.555936353271191</v>
+        <v>1.220099053751845</v>
       </c>
     </row>
     <row r="48">
@@ -959,7 +959,7 @@
         <v>1.08695652173913</v>
       </c>
       <c r="C48" t="n">
-        <v>1.493657427408387</v>
+        <v>1.177629859574361</v>
       </c>
     </row>
     <row r="49">
@@ -970,7 +970,7 @@
         <v>1.063829787234043</v>
       </c>
       <c r="C49" t="n">
-        <v>1.449639302873169</v>
+        <v>1.145878631678949</v>
       </c>
     </row>
     <row r="50">
@@ -981,7 +981,7 @@
         <v>1.041666666666667</v>
       </c>
       <c r="C50" t="n">
-        <v>1.345671787146385</v>
+        <v>1.082493135675268</v>
       </c>
     </row>
     <row r="51">
@@ -992,7 +992,7 @@
         <v>1.020408163265306</v>
       </c>
       <c r="C51" t="n">
-        <v>1.264080080261172</v>
+        <v>1.013291870813811</v>
       </c>
     </row>
     <row r="52">
@@ -1003,7 +1003,7 @@
         <v>1</v>
       </c>
       <c r="C52" t="n">
-        <v>1.20180267506601</v>
+        <v>0.9628492477647308</v>
       </c>
     </row>
     <row r="53">
@@ -1014,7 +1014,7 @@
         <v>0.9803921568627451</v>
       </c>
       <c r="C53" t="n">
-        <v>1.132865858948054</v>
+        <v>0.9130005075602564</v>
       </c>
     </row>
     <row r="54">
@@ -1025,7 +1025,7 @@
         <v>0.9615384615384615</v>
       </c>
       <c r="C54" t="n">
-        <v>1.068388444486188</v>
+        <v>0.8655284174742802</v>
       </c>
     </row>
     <row r="55">
@@ -1036,7 +1036,7 @@
         <v>0.9433962264150942</v>
       </c>
       <c r="C55" t="n">
-        <v>1.020772869127159</v>
+        <v>0.8286330412775706</v>
       </c>
     </row>
     <row r="56">
@@ -1047,7 +1047,7 @@
         <v>0.9259259259259258</v>
       </c>
       <c r="C56" t="n">
-        <v>0.9757826668364362</v>
+        <v>0.7914996127218031</v>
       </c>
     </row>
     <row r="57">
@@ -1058,7 +1058,7 @@
         <v>0.9090909090909091</v>
       </c>
       <c r="C57" t="n">
-        <v>0.936767082790669</v>
+        <v>0.7581368829569575</v>
       </c>
     </row>
     <row r="58">
@@ -1069,7 +1069,7 @@
         <v>0.8928571428571428</v>
       </c>
       <c r="C58" t="n">
-        <v>0.9167479193475222</v>
+        <v>0.7424861457034413</v>
       </c>
     </row>
     <row r="59">
@@ -1080,7 +1080,7 @@
         <v>0.8771929824561403</v>
       </c>
       <c r="C59" t="n">
-        <v>0.9060139072299763</v>
+        <v>0.7237183553474669</v>
       </c>
     </row>
     <row r="60">
@@ -1091,7 +1091,7 @@
         <v>0.8620689655172414</v>
       </c>
       <c r="C60" t="n">
-        <v>0.889089476830632</v>
+        <v>0.6991855700766473</v>
       </c>
     </row>
     <row r="61">
@@ -1102,7 +1102,7 @@
         <v>0.8474576271186441</v>
       </c>
       <c r="C61" t="n">
-        <v>0.8565377390955971</v>
+        <v>0.6682620667752242</v>
       </c>
     </row>
     <row r="62">
@@ -1113,7 +1113,7 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="C62" t="n">
-        <v>0.8161557479386742</v>
+        <v>0.6377607114602859</v>
       </c>
     </row>
     <row r="63">
@@ -1124,7 +1124,7 @@
         <v>0.819672131147541</v>
       </c>
       <c r="C63" t="n">
-        <v>0.7800468137519276</v>
+        <v>0.6178910122042283</v>
       </c>
     </row>
     <row r="64">
@@ -1135,7 +1135,7 @@
         <v>0.8064516129032259</v>
       </c>
       <c r="C64" t="n">
-        <v>0.7377541088690953</v>
+        <v>0.5960972781710523</v>
       </c>
     </row>
     <row r="65">
@@ -1146,7 +1146,7 @@
         <v>0.7936507936507936</v>
       </c>
       <c r="C65" t="n">
-        <v>0.7064941772072812</v>
+        <v>0.5715772445228667</v>
       </c>
     </row>
     <row r="66">
@@ -1157,7 +1157,7 @@
         <v>0.78125</v>
       </c>
       <c r="C66" t="n">
-        <v>0.6740048825237153</v>
+        <v>0.5453958649190287</v>
       </c>
     </row>
     <row r="67">
@@ -1168,7 +1168,7 @@
         <v>0.7692307692307692</v>
       </c>
       <c r="C67" t="n">
-        <v>0.6474113977583942</v>
+        <v>0.5247774530055727</v>
       </c>
     </row>
     <row r="68">
@@ -1179,7 +1179,7 @@
         <v>0.7575757575757576</v>
       </c>
       <c r="C68" t="n">
-        <v>0.6247173064300181</v>
+        <v>0.5077269473841866</v>
       </c>
     </row>
     <row r="69">
@@ -1190,7 +1190,7 @@
         <v>0.7462686567164178</v>
       </c>
       <c r="C69" t="n">
-        <v>0.6003836719903914</v>
+        <v>0.4887248183474932</v>
       </c>
     </row>
     <row r="70">
@@ -1201,7 +1201,7 @@
         <v>0.7352941176470588</v>
       </c>
       <c r="C70" t="n">
-        <v>0.5752581620902161</v>
+        <v>0.468822017056019</v>
       </c>
     </row>
     <row r="71">
@@ -1212,7 +1212,7 @@
         <v>0.7246376811594202</v>
       </c>
       <c r="C71" t="n">
-        <v>0.5562177848692761</v>
+        <v>0.454902583459698</v>
       </c>
     </row>
     <row r="72">
@@ -1223,7 +1223,7 @@
         <v>0.7142857142857142</v>
       </c>
       <c r="C72" t="n">
-        <v>0.538731247960762</v>
+        <v>0.442260508880316</v>
       </c>
     </row>
     <row r="73">
@@ -1234,7 +1234,7 @@
         <v>0.7042253521126761</v>
       </c>
       <c r="C73" t="n">
-        <v>0.5219489685633282</v>
+        <v>0.430022954664794</v>
       </c>
     </row>
     <row r="74">
@@ -1245,7 +1245,7 @@
         <v>0.6944444444444444</v>
       </c>
       <c r="C74" t="n">
-        <v>0.5058450623758181</v>
+        <v>0.418163288124916</v>
       </c>
     </row>
     <row r="75">
@@ -1256,7 +1256,7 @@
         <v>0.684931506849315</v>
       </c>
       <c r="C75" t="n">
-        <v>0.4906862799568035</v>
+        <v>0.4069869929039572</v>
       </c>
     </row>
     <row r="76">
@@ -1267,7 +1267,7 @@
         <v>0.6756756756756757</v>
       </c>
       <c r="C76" t="n">
-        <v>0.4779348874527162</v>
+        <v>0.3980862940294396</v>
       </c>
     </row>
     <row r="77">
@@ -1278,7 +1278,7 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="C77" t="n">
-        <v>0.4656952874426128</v>
+        <v>0.3894801290482373</v>
       </c>
     </row>
     <row r="78">
@@ -1289,7 +1289,7 @@
         <v>0.6578947368421053</v>
       </c>
       <c r="C78" t="n">
-        <v>0.4539381035440077</v>
+        <v>0.381177514438206</v>
       </c>
     </row>
     <row r="79">
@@ -1300,7 +1300,7 @@
         <v>0.6493506493506493</v>
       </c>
       <c r="C79" t="n">
-        <v>0.4426350887389564</v>
+        <v>0.3731917989044305</v>
       </c>
     </row>
     <row r="80">
@@ -1311,7 +1311,7 @@
         <v>0.641025641025641</v>
       </c>
       <c r="C80" t="n">
-        <v>0.4317690880901862</v>
+        <v>0.365536189827644</v>
       </c>
     </row>
     <row r="81">
@@ -1322,7 +1322,7 @@
         <v>0.6329113924050632</v>
       </c>
       <c r="C81" t="n">
-        <v>0.421306988248102</v>
+        <v>0.3582000387412106</v>
       </c>
     </row>
     <row r="82">
@@ -1333,7 +1333,7 @@
         <v>0.625</v>
       </c>
       <c r="C82" t="n">
-        <v>0.4112209993449211</v>
+        <v>0.3511330468463968</v>
       </c>
     </row>
     <row r="83">
@@ -1344,7 +1344,7 @@
         <v>0.6172839506172839</v>
       </c>
       <c r="C83" t="n">
-        <v>0.4014877409614384</v>
+        <v>0.3442666525102255</v>
       </c>
     </row>
     <row r="84">
@@ -1355,7 +1355,7 @@
         <v>0.6097560975609756</v>
       </c>
       <c r="C84" t="n">
-        <v>0.3920852589780976</v>
+        <v>0.3375364837563116</v>
       </c>
     </row>
     <row r="85">
@@ -1366,7 +1366,7 @@
         <v>0.6024096385542168</v>
       </c>
       <c r="C85" t="n">
-        <v>0.3829931420907001</v>
+        <v>0.3308879642638029</v>
       </c>
     </row>
     <row r="86">
@@ -1377,7 +1377,7 @@
         <v>0.5952380952380952</v>
       </c>
       <c r="C86" t="n">
-        <v>0.3741926359995189</v>
+        <v>0.3242298386035689</v>
       </c>
     </row>
     <row r="87">
@@ -1388,7 +1388,7 @@
         <v>0.5882352941176471</v>
       </c>
       <c r="C87" t="n">
-        <v>0.3656667386055658</v>
+        <v>0.3175397257372117</v>
       </c>
     </row>
     <row r="88">
@@ -1399,7 +1399,7 @@
         <v>0.5813953488372093</v>
       </c>
       <c r="C88" t="n">
-        <v>0.3574002612019169</v>
+        <v>0.3107596573391609</v>
       </c>
     </row>
     <row r="89">
@@ -1410,7 +1410,7 @@
         <v>0.5747126436781609</v>
       </c>
       <c r="C89" t="n">
-        <v>0.349379844471113</v>
+        <v>0.3039019365675392</v>
       </c>
     </row>
     <row r="90">
@@ -1421,7 +1421,7 @@
         <v>0.5681818181818182</v>
       </c>
       <c r="C90" t="n">
-        <v>0.3415939232281059</v>
+        <v>0.2969568961954478</v>
       </c>
     </row>
     <row r="91">
@@ -1432,7 +1432,7 @@
         <v>0.5617977528089888</v>
       </c>
       <c r="C91" t="n">
-        <v>0.3354575544404367</v>
+        <v>0.29009686493448</v>
       </c>
     </row>
     <row r="92">
@@ -1443,7 +1443,7 @@
         <v>0.5555555555555556</v>
       </c>
       <c r="C92" t="n">
-        <v>0.3295182369241912</v>
+        <v>0.2842135431486375</v>
       </c>
     </row>
     <row r="93">
@@ -1454,7 +1454,7 @@
         <v>0.5494505494505494</v>
       </c>
       <c r="C93" t="n">
-        <v>0.3236046209688352</v>
+        <v>0.279218948081674</v>
       </c>
     </row>
     <row r="94">
@@ -1465,7 +1465,7 @@
         <v>0.5434782608695652</v>
       </c>
       <c r="C94" t="n">
-        <v>0.3176843977824559</v>
+        <v>0.2744027944385423</v>
       </c>
     </row>
     <row r="95">
@@ -1476,7 +1476,7 @@
         <v>0.5376344086021505</v>
       </c>
       <c r="C95" t="n">
-        <v>0.3117290507344435</v>
+        <v>0.269490477364792</v>
       </c>
     </row>
     <row r="96">
@@ -1487,7 +1487,7 @@
         <v>0.5319148936170213</v>
       </c>
       <c r="C96" t="n">
-        <v>0.3057162021751379</v>
+        <v>0.2645123327772841</v>
       </c>
     </row>
     <row r="97">
@@ -1498,7 +1498,7 @@
         <v>0.5263157894736842</v>
       </c>
       <c r="C97" t="n">
-        <v>0.2996311661986636</v>
+        <v>0.2594698931108881</v>
       </c>
     </row>
     <row r="98">
@@ -1509,7 +1509,7 @@
         <v>0.5208333333333334</v>
       </c>
       <c r="C98" t="n">
-        <v>0.2934677048436283</v>
+        <v>0.2543833337039801</v>
       </c>
     </row>
     <row r="99">
@@ -1520,7 +1520,7 @@
         <v>0.5154639175257733</v>
       </c>
       <c r="C99" t="n">
-        <v>0.2872280559748516</v>
+        <v>0.2492878510403196</v>
       </c>
     </row>
     <row r="100">
@@ -1531,7 +1531,7 @@
         <v>0.5102040816326531</v>
       </c>
       <c r="C100" t="n">
-        <v>0.2809223497294466</v>
+        <v>0.2441887539554189</v>
       </c>
     </row>
     <row r="101">
@@ -1542,7 +1542,7 @@
         <v>0.5050505050505051</v>
       </c>
       <c r="C101" t="n">
-        <v>0.2745675577065596</v>
+        <v>0.2391199007448934</v>
       </c>
     </row>
     <row r="102">
@@ -1553,7 +1553,7 @@
         <v>0.5</v>
       </c>
       <c r="C102" t="n">
-        <v>0.2681861277522768</v>
+        <v>0.2340964752139003</v>
       </c>
     </row>
     <row r="103">
@@ -1564,7 +1564,7 @@
         <v>0.495049504950495</v>
       </c>
       <c r="C103" t="n">
-        <v>0.2618130428874326</v>
+        <v>0.2291302399136178</v>
       </c>
     </row>
     <row r="104">
@@ -1575,7 +1575,7 @@
         <v>0.4901960784313725</v>
       </c>
       <c r="C104" t="n">
-        <v>0.2554694725977629</v>
+        <v>0.2242475192530521</v>
       </c>
     </row>
     <row r="105">
@@ -1586,7 +1586,7 @@
         <v>0.4854368932038835</v>
       </c>
       <c r="C105" t="n">
-        <v>0.2491825441951814</v>
+        <v>0.2194489296412251</v>
       </c>
     </row>
     <row r="106">
@@ -1597,7 +1597,7 @@
         <v>0.4807692307692307</v>
       </c>
       <c r="C106" t="n">
-        <v>0.2440814898509022</v>
+        <v>0.2147503007932816</v>
       </c>
     </row>
     <row r="107">
@@ -1608,7 +1608,7 @@
         <v>0.4761904761904762</v>
       </c>
       <c r="C107" t="n">
-        <v>0.2408258848216604</v>
+        <v>0.2101876634244539</v>
       </c>
     </row>
     <row r="108">
@@ -1619,7 +1619,7 @@
         <v>0.4716981132075471</v>
       </c>
       <c r="C108" t="n">
-        <v>0.238050465859597</v>
+        <v>0.2059766241928694</v>
       </c>
     </row>
     <row r="109">
@@ -1630,7 +1630,7 @@
         <v>0.4672897196261682</v>
       </c>
       <c r="C109" t="n">
-        <v>0.2352305343661629</v>
+        <v>0.2023893260696357</v>
       </c>
     </row>
     <row r="110">
@@ -1641,7 +1641,7 @@
         <v>0.4629629629629629</v>
       </c>
       <c r="C110" t="n">
-        <v>0.2323553954695444</v>
+        <v>0.1988779758385557</v>
       </c>
     </row>
     <row r="111">
@@ -1652,7 +1652,7 @@
         <v>0.4587155963302752</v>
       </c>
       <c r="C111" t="n">
-        <v>0.2294206225240106</v>
+        <v>0.1954415997467808</v>
       </c>
     </row>
     <row r="112">
@@ -1663,7 +1663,7 @@
         <v>0.4545454545454545</v>
       </c>
       <c r="C112" t="n">
-        <v>0.2264270394367913</v>
+        <v>0.1920811387400201</v>
       </c>
     </row>
     <row r="113">
@@ -1674,7 +1674,7 @@
         <v>0.4504504504504504</v>
       </c>
       <c r="C113" t="n">
-        <v>0.2233801975286696</v>
+        <v>0.1887924281077063</v>
       </c>
     </row>
     <row r="114">
@@ -1685,7 +1685,7 @@
         <v>0.4464285714285714</v>
       </c>
       <c r="C114" t="n">
-        <v>0.2202776598726474</v>
+        <v>0.1858248899558066</v>
       </c>
     </row>
     <row r="115">
@@ -1696,7 +1696,7 @@
         <v>0.4424778761061947</v>
       </c>
       <c r="C115" t="n">
-        <v>0.2171255718653057</v>
+        <v>0.1829494586930759</v>
       </c>
     </row>
     <row r="116">
@@ -1707,7 +1707,7 @@
         <v>0.4385964912280702</v>
       </c>
       <c r="C116" t="n">
-        <v>0.2139418834185264</v>
+        <v>0.180137513506511</v>
       </c>
     </row>
     <row r="117">
@@ -1718,7 +1718,7 @@
         <v>0.4347826086956521</v>
       </c>
       <c r="C117" t="n">
-        <v>0.2107221130204365</v>
+        <v>0.1773848272141608</v>
       </c>
     </row>
     <row r="118">
@@ -1729,7 +1729,7 @@
         <v>0.4310344827586207</v>
       </c>
       <c r="C118" t="n">
-        <v>0.2074744821320522</v>
+        <v>0.1746872518967459</v>
       </c>
     </row>
     <row r="119">
@@ -1740,7 +1740,7 @@
         <v>0.4273504273504274</v>
       </c>
       <c r="C119" t="n">
-        <v>0.2042074428787813</v>
+        <v>0.1720407964606915</v>
       </c>
     </row>
     <row r="120">
@@ -1751,7 +1751,7 @@
         <v>0.4237288135593221</v>
       </c>
       <c r="C120" t="n">
-        <v>0.200929411751521</v>
+        <v>0.1694416905577522</v>
       </c>
     </row>
     <row r="121">
@@ -1762,7 +1762,7 @@
         <v>0.4201680672268908</v>
       </c>
       <c r="C121" t="n">
-        <v>0.19764855702591</v>
+        <v>0.1668864348636357</v>
       </c>
     </row>
     <row r="122">
@@ -1773,7 +1773,7 @@
         <v>0.4166666666666667</v>
       </c>
       <c r="C122" t="n">
-        <v>0.1943726367040498</v>
+        <v>0.1643718382718428</v>
       </c>
     </row>
     <row r="123">
@@ -1784,7 +1784,7 @@
         <v>0.4132231404958678</v>
       </c>
       <c r="C123" t="n">
-        <v>0.191108882288917</v>
+        <v>0.1618950428593282</v>
       </c>
     </row>
     <row r="124">
@@ -1795,7 +1795,7 @@
         <v>0.4098360655737705</v>
       </c>
       <c r="C124" t="n">
-        <v>0.1878639228652063</v>
+        <v>0.1594535377565672</v>
       </c>
     </row>
     <row r="125">
@@ -1806,7 +1806,7 @@
         <v>0.4065040650406504</v>
       </c>
       <c r="C125" t="n">
-        <v>0.1846437434999004</v>
+        <v>0.1570451631845396</v>
       </c>
     </row>
     <row r="126">
@@ -1817,7 +1817,7 @@
         <v>0.4032258064516129</v>
       </c>
       <c r="C126" t="n">
-        <v>0.1814536719644522</v>
+        <v>0.1546681060269992</v>
       </c>
     </row>
     <row r="127">
@@ -1828,7 +1828,7 @@
         <v>0.4</v>
       </c>
       <c r="C127" t="n">
-        <v>0.1783023663386534</v>
+        <v>0.1523208882912999</v>
       </c>
     </row>
     <row r="128">
@@ -1839,7 +1839,7 @@
         <v>0.3968253968253968</v>
       </c>
       <c r="C128" t="n">
-        <v>0.1751891813537757</v>
+        <v>0.150002349813928</v>
       </c>
     </row>
     <row r="129">
@@ -1850,7 +1850,7 @@
         <v>0.3937007874015748</v>
       </c>
       <c r="C129" t="n">
-        <v>0.1721175984141954</v>
+        <v>0.1477116264712651</v>
       </c>
     </row>
     <row r="130">
@@ -1861,7 +1861,7 @@
         <v>0.390625</v>
       </c>
       <c r="C130" t="n">
-        <v>0.1690906079568013</v>
+        <v>0.1454481250697862</v>
       </c>
     </row>
     <row r="131">
@@ -1872,7 +1872,7 @@
         <v>0.3875968992248062</v>
       </c>
       <c r="C131" t="n">
-        <v>0.1661107144642788</v>
+        <v>0.1432114959837913</v>
       </c>
     </row>
     <row r="132">
@@ -1883,7 +1883,7 @@
         <v>0.3846153846153846</v>
       </c>
       <c r="C132" t="n">
-        <v>0.1631800027962835</v>
+        <v>0.1410016185218426</v>
       </c>
     </row>
     <row r="133">
@@ -1894,7 +1894,7 @@
         <v>0.3816793893129771</v>
       </c>
       <c r="C133" t="n">
-        <v>0.1603008342743404</v>
+        <v>0.1388192159533398</v>
       </c>
     </row>
     <row r="134">
@@ -1905,7 +1905,7 @@
         <v>0.3787878787878788</v>
       </c>
       <c r="C134" t="n">
-        <v>0.1574738988002561</v>
+        <v>0.1366638289277</v>
       </c>
     </row>
     <row r="135">
@@ -1916,7 +1916,7 @@
         <v>0.3759398496240601</v>
       </c>
       <c r="C135" t="n">
-        <v>0.154700269065503</v>
+        <v>0.1345357951850283</v>
       </c>
     </row>
     <row r="136">
@@ -1927,7 +1927,7 @@
         <v>0.3731343283582089</v>
       </c>
       <c r="C136" t="n">
-        <v>0.1519807739203538</v>
+        <v>0.1324355539204029</v>
       </c>
     </row>
     <row r="137">
@@ -1938,7 +1938,7 @@
         <v>0.3703703703703703</v>
       </c>
       <c r="C137" t="n">
-        <v>0.1493160356341941</v>
+        <v>0.1303830118340421</v>
       </c>
     </row>
     <row r="138">
@@ -1949,7 +1949,7 @@
         <v>0.3676470588235294</v>
       </c>
       <c r="C138" t="n">
-        <v>0.1467124932198392</v>
+        <v>0.1287109089957128</v>
       </c>
     </row>
     <row r="139">
@@ -1960,7 +1960,7 @@
         <v>0.364963503649635</v>
       </c>
       <c r="C139" t="n">
-        <v>0.1441643977653418</v>
+        <v>0.1269791020148727</v>
       </c>
     </row>
     <row r="140">
@@ -1971,7 +1971,7 @@
         <v>0.3623188405797101</v>
       </c>
       <c r="C140" t="n">
-        <v>0.1416718343406093</v>
+        <v>0.1251798270734296</v>
       </c>
     </row>
     <row r="141">
@@ -1982,7 +1982,7 @@
         <v>0.3597122302158273</v>
       </c>
       <c r="C141" t="n">
-        <v>0.1392348793034633</v>
+        <v>0.1237647458976231</v>
       </c>
     </row>
     <row r="142">
@@ -1993,7 +1993,7 @@
         <v>0.3571428571428571</v>
       </c>
       <c r="C142" t="n">
-        <v>0.1370568659420044</v>
+        <v>0.1224106272928428</v>
       </c>
     </row>
     <row r="143">
@@ -2004,7 +2004,7 @@
         <v>0.3546099290780142</v>
       </c>
       <c r="C143" t="n">
-        <v>0.1351236872314516</v>
+        <v>0.1209965321179503</v>
       </c>
     </row>
     <row r="144">
@@ -2015,7 +2015,7 @@
         <v>0.3521126760563381</v>
       </c>
       <c r="C144" t="n">
-        <v>0.1332278701221142</v>
+        <v>0.1195085166047825</v>
       </c>
     </row>
     <row r="145">
@@ -2026,7 +2026,7 @@
         <v>0.3496503496503497</v>
       </c>
       <c r="C145" t="n">
-        <v>0.1313688423595479</v>
+        <v>0.1179442383295577</v>
       </c>
     </row>
     <row r="146">
@@ -2037,7 +2037,7 @@
         <v>0.3472222222222222</v>
       </c>
       <c r="C146" t="n">
-        <v>0.1295487861330799</v>
+        <v>0.1163154600389245</v>
       </c>
     </row>
     <row r="147">
@@ -2048,7 +2048,7 @@
         <v>0.3448275862068966</v>
       </c>
       <c r="C147" t="n">
-        <v>0.1277663791500516</v>
+        <v>0.1147033870577248</v>
       </c>
     </row>
     <row r="148">
@@ -2059,7 +2059,7 @@
         <v>0.3424657534246575</v>
       </c>
       <c r="C148" t="n">
-        <v>0.1260210317984343</v>
+        <v>0.11326296511777</v>
       </c>
     </row>
     <row r="149">
@@ -2070,7 +2070,7 @@
         <v>0.3401360544217687</v>
       </c>
       <c r="C149" t="n">
-        <v>0.1243128668394189</v>
+        <v>0.1118077644813729</v>
       </c>
     </row>
     <row r="150">
@@ -2081,7 +2081,7 @@
         <v>0.3378378378378378</v>
       </c>
       <c r="C150" t="n">
-        <v>0.1226384395380234</v>
+        <v>0.1103370149884912</v>
       </c>
     </row>
     <row r="151">
@@ -2092,7 +2092,7 @@
         <v>0.3355704697986577</v>
       </c>
       <c r="C151" t="n">
-        <v>0.1209971757264594</v>
+        <v>0.1088532731181895</v>
       </c>
     </row>
     <row r="152">
@@ -2103,7 +2103,7 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="C152" t="n">
-        <v>0.1193884958566753</v>
+        <v>0.1073614011176534</v>
       </c>
     </row>
     <row r="153">
@@ -2114,7 +2114,7 @@
         <v>0.3311258278145696</v>
       </c>
       <c r="C153" t="n">
-        <v>0.1178118149081866</v>
+        <v>0.1058650375848483</v>
       </c>
     </row>
     <row r="154">
@@ -2125,7 +2125,7 @@
         <v>0.3289473684210527</v>
       </c>
       <c r="C154" t="n">
-        <v>0.1162665426089842</v>
+        <v>0.104364748435589</v>
       </c>
     </row>
     <row r="155">
@@ -2136,7 +2136,7 @@
         <v>0.326797385620915</v>
       </c>
       <c r="C155" t="n">
-        <v>0.1147520838870105</v>
+        <v>0.1028639106520703</v>
       </c>
     </row>
     <row r="156">
@@ -2147,7 +2147,7 @@
         <v>0.3246753246753247</v>
       </c>
       <c r="C156" t="n">
-        <v>0.1132678395450239</v>
+        <v>0.1013659108150026</v>
       </c>
     </row>
     <row r="157">
@@ -2158,7 +2158,7 @@
         <v>0.3225806451612903</v>
       </c>
       <c r="C157" t="n">
-        <v>0.111813207063936</v>
+        <v>0.09987407961942159</v>
       </c>
     </row>
     <row r="158">
@@ -2169,7 +2169,7 @@
         <v>0.3205128205128205</v>
       </c>
       <c r="C158" t="n">
-        <v>0.1103875815469547</v>
+        <v>0.09839379203810639</v>
       </c>
     </row>
     <row r="159">
@@ -2180,7 +2180,7 @@
         <v>0.3184713375796178</v>
       </c>
       <c r="C159" t="n">
-        <v>0.1089903567229595</v>
+        <v>0.09721398871822416</v>
       </c>
     </row>
     <row r="160">
@@ -2191,7 +2191,7 @@
         <v>0.3164556962025316</v>
       </c>
       <c r="C160" t="n">
-        <v>0.1076209260196788</v>
+        <v>0.09603646492626217</v>
       </c>
     </row>
     <row r="161">
@@ -2202,7 +2202,7 @@
         <v>0.3144654088050314</v>
       </c>
       <c r="C161" t="n">
-        <v>0.1062786836399266</v>
+        <v>0.09484172796445757</v>
       </c>
     </row>
     <row r="162">
@@ -2213,7 +2213,7 @@
         <v>0.3125</v>
       </c>
       <c r="C162" t="n">
-        <v>0.1049630256613523</v>
+        <v>0.09363331814128512</v>
       </c>
     </row>
     <row r="163">
@@ -2224,7 +2224,7 @@
         <v>0.3105590062111801</v>
       </c>
       <c r="C163" t="n">
-        <v>0.1036733511022629</v>
+        <v>0.0924148780332735</v>
       </c>
     </row>
     <row r="164">
@@ -2235,7 +2235,7 @@
         <v>0.308641975308642</v>
       </c>
       <c r="C164" t="n">
-        <v>0.1024090629686595</v>
+        <v>0.0911901266089753</v>
       </c>
     </row>
     <row r="165">
@@ -2246,7 +2246,7 @@
         <v>0.3067484662576687</v>
       </c>
       <c r="C165" t="n">
-        <v>0.1011695692484961</v>
+        <v>0.08996607091463495</v>
       </c>
     </row>
     <row r="166">
@@ -2257,7 +2257,7 @@
         <v>0.3048780487804878</v>
       </c>
       <c r="C166" t="n">
-        <v>0.09995428385458184</v>
+        <v>0.08874239029348983</v>
       </c>
     </row>
     <row r="167">
@@ -2268,7 +2268,7 @@
         <v>0.303030303030303</v>
       </c>
       <c r="C167" t="n">
-        <v>0.09876262750935726</v>
+        <v>0.08767209700668394</v>
       </c>
     </row>
     <row r="168">
@@ -2279,7 +2279,7 @@
         <v>0.3012048192771084</v>
       </c>
       <c r="C168" t="n">
-        <v>0.09759402855886891</v>
+        <v>0.08661459054915153</v>
       </c>
     </row>
     <row r="169">
@@ -2290,7 +2290,7 @@
         <v>0.2994011976047904</v>
       </c>
       <c r="C169" t="n">
-        <v>0.09644808939183536</v>
+        <v>0.0855620176818067</v>
       </c>
     </row>
     <row r="170">
@@ -2301,7 +2301,7 @@
         <v>0.2976190476190476</v>
       </c>
       <c r="C170" t="n">
-        <v>0.09532787419545247</v>
+        <v>0.08451792491313226</v>
       </c>
     </row>
     <row r="171">
@@ -2312,7 +2312,7 @@
         <v>0.2958579881656805</v>
       </c>
       <c r="C171" t="n">
-        <v>0.09423093821597642</v>
+        <v>0.08348372363888028</v>
       </c>
     </row>
     <row r="172">
@@ -2323,7 +2323,7 @@
         <v>0.2941176470588235</v>
       </c>
       <c r="C172" t="n">
-        <v>0.09315665938565455</v>
+        <v>0.08246084520662506</v>
       </c>
     </row>
     <row r="173">
@@ -2334,7 +2334,7 @@
         <v>0.2923976608187134</v>
       </c>
       <c r="C173" t="n">
-        <v>0.09210254703793207</v>
+        <v>0.08144869486402966</v>
       </c>
     </row>
     <row r="174">
@@ -2345,7 +2345,7 @@
         <v>0.2906976744186047</v>
       </c>
       <c r="C174" t="n">
-        <v>0.09106809258197339</v>
+        <v>0.0804484966585611</v>
       </c>
     </row>
     <row r="175">
@@ -2356,7 +2356,7 @@
         <v>0.2890173410404624</v>
       </c>
       <c r="C175" t="n">
-        <v>0.09005279861670638</v>
+        <v>0.07946846887882994</v>
       </c>
     </row>
     <row r="176">
@@ -2367,7 +2367,7 @@
         <v>0.2873563218390804</v>
       </c>
       <c r="C176" t="n">
-        <v>0.08905617919120211</v>
+        <v>0.07856092692709904</v>
       </c>
     </row>
     <row r="177">
@@ -2378,7 +2378,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="C177" t="n">
-        <v>0.08807776000391962</v>
+        <v>0.07766665152579845</v>
       </c>
     </row>
     <row r="178">
@@ -2389,7 +2389,7 @@
         <v>0.2840909090909091</v>
       </c>
       <c r="C178" t="n">
-        <v>0.08711707854902649</v>
+        <v>0.07678581388983101</v>
       </c>
     </row>
     <row r="179">
@@ -2400,7 +2400,7 @@
         <v>0.2824858757062147</v>
       </c>
       <c r="C179" t="n">
-        <v>0.08617368420014067</v>
+        <v>0.07591854608690396</v>
       </c>
     </row>
     <row r="180">
@@ -2411,7 +2411,7 @@
         <v>0.2808988764044944</v>
       </c>
       <c r="C180" t="n">
-        <v>0.08524713825846826</v>
+        <v>0.07506494180023379</v>
       </c>
     </row>
     <row r="181">
@@ -2422,7 +2422,7 @@
         <v>0.2793296089385475</v>
       </c>
       <c r="C181" t="n">
-        <v>0.08433871334427279</v>
+        <v>0.07422675684586508</v>
       </c>
     </row>
     <row r="182">
@@ -2433,7 +2433,7 @@
         <v>0.2777777777777778</v>
       </c>
       <c r="C182" t="n">
-        <v>0.08344756133881601</v>
+        <v>0.07340357858765076</v>
       </c>
     </row>
     <row r="183">
@@ -2444,7 +2444,7 @@
         <v>0.2762430939226519</v>
       </c>
       <c r="C183" t="n">
-        <v>0.08257194523506638</v>
+        <v>0.07259405954926737</v>
       </c>
     </row>
     <row r="184">
@@ -2455,7 +2455,7 @@
         <v>0.2747252747252747</v>
       </c>
       <c r="C184" t="n">
-        <v>0.0817114753784277</v>
+        <v>0.07179815564810925</v>
       </c>
     </row>
     <row r="185">
@@ -2466,7 +2466,7 @@
         <v>0.273224043715847</v>
       </c>
       <c r="C185" t="n">
-        <v>0.08086577359642985</v>
+        <v>0.07101579250147978</v>
       </c>
     </row>
     <row r="186">
@@ -2477,7 +2477,7 @@
         <v>0.2717391304347826</v>
       </c>
       <c r="C186" t="n">
-        <v>0.08003447302744843</v>
+        <v>0.07024686757025123</v>
       </c>
     </row>
     <row r="187">
@@ -2488,7 +2488,7 @@
         <v>0.2702702702702702</v>
       </c>
       <c r="C187" t="n">
-        <v>0.07921721792550712</v>
+        <v>0.06949125237353757</v>
       </c>
     </row>
     <row r="188">
@@ -2499,7 +2499,7 @@
         <v>0.2688172043010753</v>
       </c>
       <c r="C188" t="n">
-        <v>0.07841366344596663</v>
+        <v>0.06874970491302602</v>
       </c>
     </row>
     <row r="189">
@@ -2510,7 +2510,7 @@
         <v>0.267379679144385</v>
       </c>
       <c r="C189" t="n">
-        <v>0.07762347540730825</v>
+        <v>0.06804002130866735</v>
       </c>
     </row>
     <row r="190">
@@ -2521,7 +2521,7 @@
         <v>0.2659574468085106</v>
       </c>
       <c r="C190" t="n">
-        <v>0.07684633005292012</v>
+        <v>0.06734270426983953</v>
       </c>
     </row>
     <row r="191">
@@ -2532,7 +2532,7 @@
         <v>0.2645502645502645</v>
       </c>
       <c r="C191" t="n">
-        <v>0.07608191378761928</v>
+        <v>0.06665749875130045</v>
       </c>
     </row>
     <row r="192">
@@ -2543,7 +2543,7 @@
         <v>0.2631578947368421</v>
       </c>
       <c r="C192" t="n">
-        <v>0.07532992291347211</v>
+        <v>0.06598415346506696</v>
       </c>
     </row>
     <row r="193">
@@ -2554,7 +2554,7 @@
         <v>0.2617801047120419</v>
       </c>
       <c r="C193" t="n">
-        <v>0.07459006335454985</v>
+        <v>0.06532242098821427</v>
       </c>
     </row>
     <row r="194">
@@ -2565,7 +2565,7 @@
         <v>0.2604166666666667</v>
       </c>
       <c r="C194" t="n">
-        <v>0.07386205038004716</v>
+        <v>0.06467205785676552</v>
       </c>
     </row>
     <row r="195">
@@ -2576,7 +2576,7 @@
         <v>0.2590673575129534</v>
       </c>
       <c r="C195" t="n">
-        <v>0.07314560832424873</v>
+        <v>0.06403282464303885</v>
       </c>
     </row>
     <row r="196">
@@ -2587,7 +2587,7 @@
         <v>0.2577319587628866</v>
       </c>
       <c r="C196" t="n">
-        <v>0.07244047029689496</v>
+        <v>0.06340448601200876</v>
       </c>
     </row>
     <row r="197">
@@ -2598,7 +2598,7 @@
         <v>0.2564102564102564</v>
       </c>
       <c r="C197" t="n">
-        <v>0.07174637790766196</v>
+        <v>0.06278681077569982</v>
       </c>
     </row>
     <row r="198">
@@ -2609,7 +2609,7 @@
         <v>0.2551020408163265</v>
       </c>
       <c r="C198" t="n">
-        <v>0.07106386835223157</v>
+        <v>0.06218035929798766</v>
       </c>
     </row>
     <row r="199">
@@ -2620,7 +2620,7 @@
         <v>0.2538071065989848</v>
       </c>
       <c r="C199" t="n">
-        <v>0.07050778002613667</v>
+        <v>0.06158578558075654</v>
       </c>
     </row>
     <row r="200">
@@ -2631,7 +2631,7 @@
         <v>0.2525252525252525</v>
       </c>
       <c r="C200" t="n">
-        <v>0.07000318993204671</v>
+        <v>0.06100116014685178</v>
       </c>
     </row>
     <row r="201">
@@ -2642,7 +2642,7 @@
         <v>0.2512562814070352</v>
       </c>
       <c r="C201" t="n">
-        <v>0.06950584870609218</v>
+        <v>0.06042626962425181</v>
       </c>
     </row>
     <row r="202">
@@ -2653,7 +2653,7 @@
         <v>0.25</v>
       </c>
       <c r="C202" t="n">
-        <v>0.06901540673923164</v>
+        <v>0.05986090483120173</v>
       </c>
     </row>
   </sheetData>

--- a/Python for Project Work SRE_Part 2/ERS/ERS/ERS_Means/SA_el_hor1_mean.xlsx
+++ b/Python for Project Work SRE_Part 2/ERS/ERS/ERS_Means/SA_el_hor1_mean.xlsx
@@ -464,7 +464,7 @@
         <v>50</v>
       </c>
       <c r="C3" t="n">
-        <v>5.209775404733045</v>
+        <v>5.195019532217376</v>
       </c>
     </row>
     <row r="4">
@@ -475,7 +475,7 @@
         <v>25</v>
       </c>
       <c r="C4" t="n">
-        <v>5.807330645985359</v>
+        <v>5.666713890035027</v>
       </c>
     </row>
     <row r="5">
@@ -486,7 +486,7 @@
         <v>16.66666666666667</v>
       </c>
       <c r="C5" t="n">
-        <v>8.076801445082753</v>
+        <v>6.845756411933245</v>
       </c>
     </row>
     <row r="6">
@@ -497,7 +497,7 @@
         <v>12.5</v>
       </c>
       <c r="C6" t="n">
-        <v>10.06419748652128</v>
+        <v>8.297037044659222</v>
       </c>
     </row>
     <row r="7">
@@ -508,7 +508,7 @@
         <v>10</v>
       </c>
       <c r="C7" t="n">
-        <v>11.60473713523046</v>
+        <v>8.650760922154983</v>
       </c>
     </row>
     <row r="8">
@@ -519,7 +519,7 @@
         <v>8.333333333333334</v>
       </c>
       <c r="C8" t="n">
-        <v>10.74828953504452</v>
+        <v>10.74538914866522</v>
       </c>
     </row>
     <row r="9">
@@ -530,7 +530,7 @@
         <v>7.142857142857142</v>
       </c>
       <c r="C9" t="n">
-        <v>11.50210995319536</v>
+        <v>11.56363640554803</v>
       </c>
     </row>
     <row r="10">
@@ -541,7 +541,7 @@
         <v>6.25</v>
       </c>
       <c r="C10" t="n">
-        <v>10.02811736247793</v>
+        <v>11.33900760868636</v>
       </c>
     </row>
     <row r="11">
@@ -552,7 +552,7 @@
         <v>5.555555555555555</v>
       </c>
       <c r="C11" t="n">
-        <v>9.951019208968212</v>
+        <v>13.30053772572895</v>
       </c>
     </row>
     <row r="12">
@@ -563,7 +563,7 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>9.902683471929398</v>
+        <v>12.12197700527993</v>
       </c>
     </row>
     <row r="13">
@@ -574,7 +574,7 @@
         <v>4.545454545454546</v>
       </c>
       <c r="C13" t="n">
-        <v>9.855155629377238</v>
+        <v>11.5039026411518</v>
       </c>
     </row>
     <row r="14">
@@ -585,7 +585,7 @@
         <v>4.166666666666667</v>
       </c>
       <c r="C14" t="n">
-        <v>9.625604802400199</v>
+        <v>12.71703213851333</v>
       </c>
     </row>
     <row r="15">
@@ -596,7 +596,7 @@
         <v>3.846153846153846</v>
       </c>
       <c r="C15" t="n">
-        <v>9.685251316158149</v>
+        <v>12.23923919531075</v>
       </c>
     </row>
     <row r="16">
@@ -607,7 +607,7 @@
         <v>3.571428571428571</v>
       </c>
       <c r="C16" t="n">
-        <v>9.684611056147915</v>
+        <v>11.14360117975242</v>
       </c>
     </row>
     <row r="17">
@@ -618,7 +618,7 @@
         <v>3.333333333333333</v>
       </c>
       <c r="C17" t="n">
-        <v>9.534304407178576</v>
+        <v>10.78028546447998</v>
       </c>
     </row>
     <row r="18">
@@ -629,7 +629,7 @@
         <v>3.125</v>
       </c>
       <c r="C18" t="n">
-        <v>8.975236787779179</v>
+        <v>10.738599174634</v>
       </c>
     </row>
     <row r="19">
@@ -640,7 +640,7 @@
         <v>2.941176470588235</v>
       </c>
       <c r="C19" t="n">
-        <v>8.370087552133359</v>
+        <v>10.20915414420019</v>
       </c>
     </row>
     <row r="20">
@@ -651,7 +651,7 @@
         <v>2.777777777777778</v>
       </c>
       <c r="C20" t="n">
-        <v>8.049239269675491</v>
+        <v>9.579848506346845</v>
       </c>
     </row>
     <row r="21">
@@ -662,7 +662,7 @@
         <v>2.631578947368421</v>
       </c>
       <c r="C21" t="n">
-        <v>7.803353391312526</v>
+        <v>8.945989234538112</v>
       </c>
     </row>
     <row r="22">
@@ -673,7 +673,7 @@
         <v>2.5</v>
       </c>
       <c r="C22" t="n">
-        <v>7.370142035072652</v>
+        <v>8.793712618018757</v>
       </c>
     </row>
     <row r="23">
@@ -684,7 +684,7 @@
         <v>2.380952380952381</v>
       </c>
       <c r="C23" t="n">
-        <v>6.832512306022912</v>
+        <v>8.345832902339131</v>
       </c>
     </row>
     <row r="24">
@@ -695,7 +695,7 @@
         <v>2.272727272727273</v>
       </c>
       <c r="C24" t="n">
-        <v>6.161080955427107</v>
+        <v>8.43940949754748</v>
       </c>
     </row>
     <row r="25">
@@ -706,7 +706,7 @@
         <v>2.173913043478261</v>
       </c>
       <c r="C25" t="n">
-        <v>5.651819307706812</v>
+        <v>8.364960090919492</v>
       </c>
     </row>
     <row r="26">
@@ -717,7 +717,7 @@
         <v>2.083333333333333</v>
       </c>
       <c r="C26" t="n">
-        <v>5.175067063878051</v>
+        <v>7.488945125915487</v>
       </c>
     </row>
     <row r="27">
@@ -728,7 +728,7 @@
         <v>2</v>
       </c>
       <c r="C27" t="n">
-        <v>4.789925082894959</v>
+        <v>6.761309549837947</v>
       </c>
     </row>
     <row r="28">
@@ -739,7 +739,7 @@
         <v>1.923076923076923</v>
       </c>
       <c r="C28" t="n">
-        <v>4.484438047811919</v>
+        <v>6.265473987488536</v>
       </c>
     </row>
     <row r="29">
@@ -750,7 +750,7 @@
         <v>1.851851851851852</v>
       </c>
       <c r="C29" t="n">
-        <v>4.224606916782013</v>
+        <v>5.548818567504309</v>
       </c>
     </row>
     <row r="30">
@@ -761,7 +761,7 @@
         <v>1.785714285714286</v>
       </c>
       <c r="C30" t="n">
-        <v>3.99079120723384</v>
+        <v>4.857558575945526</v>
       </c>
     </row>
     <row r="31">
@@ -772,7 +772,7 @@
         <v>1.724137931034483</v>
       </c>
       <c r="C31" t="n">
-        <v>3.608471440850066</v>
+        <v>4.296641897207939</v>
       </c>
     </row>
     <row r="32">
@@ -783,7 +783,7 @@
         <v>1.666666666666667</v>
       </c>
       <c r="C32" t="n">
-        <v>3.200618076411073</v>
+        <v>3.834102692832598</v>
       </c>
     </row>
     <row r="33">
@@ -794,7 +794,7 @@
         <v>1.612903225806452</v>
       </c>
       <c r="C33" t="n">
-        <v>2.931565946113395</v>
+        <v>3.494677278921454</v>
       </c>
     </row>
     <row r="34">
@@ -805,7 +805,7 @@
         <v>1.5625</v>
       </c>
       <c r="C34" t="n">
-        <v>2.730021382237624</v>
+        <v>3.239071685877819</v>
       </c>
     </row>
     <row r="35">
@@ -816,7 +816,7 @@
         <v>1.515151515151515</v>
       </c>
       <c r="C35" t="n">
-        <v>2.465818587567659</v>
+        <v>2.960028625304515</v>
       </c>
     </row>
     <row r="36">
@@ -827,7 +827,7 @@
         <v>1.470588235294118</v>
       </c>
       <c r="C36" t="n">
-        <v>2.270367218394923</v>
+        <v>2.706368081555074</v>
       </c>
     </row>
     <row r="37">
@@ -838,7 +838,7 @@
         <v>1.428571428571428</v>
       </c>
       <c r="C37" t="n">
-        <v>2.144876002492675</v>
+        <v>2.531061440470482</v>
       </c>
     </row>
     <row r="38">
@@ -849,7 +849,7 @@
         <v>1.388888888888889</v>
       </c>
       <c r="C38" t="n">
-        <v>2.144837832403341</v>
+        <v>2.4779951774573</v>
       </c>
     </row>
     <row r="39">
@@ -860,7 +860,7 @@
         <v>1.351351351351351</v>
       </c>
       <c r="C39" t="n">
-        <v>2.156296204375916</v>
+        <v>2.458628523701802</v>
       </c>
     </row>
     <row r="40">
@@ -871,7 +871,7 @@
         <v>1.315789473684211</v>
       </c>
       <c r="C40" t="n">
-        <v>2.098666410110609</v>
+        <v>2.380587096115107</v>
       </c>
     </row>
     <row r="41">
@@ -882,7 +882,7 @@
         <v>1.282051282051282</v>
       </c>
       <c r="C41" t="n">
-        <v>1.941819518248851</v>
+        <v>2.211878102320597</v>
       </c>
     </row>
     <row r="42">
@@ -893,7 +893,7 @@
         <v>1.25</v>
       </c>
       <c r="C42" t="n">
-        <v>1.713549881140697</v>
+        <v>1.951014714541844</v>
       </c>
     </row>
     <row r="43">
@@ -904,7 +904,7 @@
         <v>1.219512195121951</v>
       </c>
       <c r="C43" t="n">
-        <v>1.530746175312632</v>
+        <v>1.772900414501172</v>
       </c>
     </row>
     <row r="44">
@@ -915,7 +915,7 @@
         <v>1.19047619047619</v>
       </c>
       <c r="C44" t="n">
-        <v>1.422758683803221</v>
+        <v>1.653729801318509</v>
       </c>
     </row>
     <row r="45">
@@ -926,7 +926,7 @@
         <v>1.162790697674419</v>
       </c>
       <c r="C45" t="n">
-        <v>1.339398831839642</v>
+        <v>1.557547615526624</v>
       </c>
     </row>
     <row r="46">
@@ -937,7 +937,7 @@
         <v>1.136363636363636</v>
       </c>
       <c r="C46" t="n">
-        <v>1.270597069784815</v>
+        <v>1.468943076723105</v>
       </c>
     </row>
     <row r="47">
@@ -948,7 +948,7 @@
         <v>1.111111111111111</v>
       </c>
       <c r="C47" t="n">
-        <v>1.220099053751845</v>
+        <v>1.39384459253155</v>
       </c>
     </row>
     <row r="48">
@@ -959,7 +959,7 @@
         <v>1.08695652173913</v>
       </c>
       <c r="C48" t="n">
-        <v>1.177629859574361</v>
+        <v>1.338066491566495</v>
       </c>
     </row>
     <row r="49">
@@ -970,7 +970,7 @@
         <v>1.063829787234043</v>
       </c>
       <c r="C49" t="n">
-        <v>1.145878631678949</v>
+        <v>1.304649735068087</v>
       </c>
     </row>
     <row r="50">
@@ -981,7 +981,7 @@
         <v>1.041666666666667</v>
       </c>
       <c r="C50" t="n">
-        <v>1.082493135675268</v>
+        <v>1.210334899631995</v>
       </c>
     </row>
     <row r="51">
@@ -992,7 +992,7 @@
         <v>1.020408163265306</v>
       </c>
       <c r="C51" t="n">
-        <v>1.013291870813811</v>
+        <v>1.137501842684704</v>
       </c>
     </row>
     <row r="52">
@@ -1003,7 +1003,7 @@
         <v>1</v>
       </c>
       <c r="C52" t="n">
-        <v>0.9628492477647308</v>
+        <v>1.084008225963671</v>
       </c>
     </row>
     <row r="53">
@@ -1014,7 +1014,7 @@
         <v>0.9803921568627451</v>
       </c>
       <c r="C53" t="n">
-        <v>0.9130005075602564</v>
+        <v>1.023463136677892</v>
       </c>
     </row>
     <row r="54">
@@ -1025,7 +1025,7 @@
         <v>0.9615384615384615</v>
       </c>
       <c r="C54" t="n">
-        <v>0.8655284174742802</v>
+        <v>0.9670744295566309</v>
       </c>
     </row>
     <row r="55">
@@ -1036,7 +1036,7 @@
         <v>0.9433962264150942</v>
       </c>
       <c r="C55" t="n">
-        <v>0.8286330412775706</v>
+        <v>0.9270287166560154</v>
       </c>
     </row>
     <row r="56">
@@ -1047,7 +1047,7 @@
         <v>0.9259259259259258</v>
       </c>
       <c r="C56" t="n">
-        <v>0.7914996127218031</v>
+        <v>0.8892295628527888</v>
       </c>
     </row>
     <row r="57">
@@ -1058,7 +1058,7 @@
         <v>0.9090909090909091</v>
       </c>
       <c r="C57" t="n">
-        <v>0.7581368829569575</v>
+        <v>0.8569245213289254</v>
       </c>
     </row>
     <row r="58">
@@ -1069,7 +1069,7 @@
         <v>0.8928571428571428</v>
       </c>
       <c r="C58" t="n">
-        <v>0.7424861457034413</v>
+        <v>0.8431700240532235</v>
       </c>
     </row>
     <row r="59">
@@ -1080,7 +1080,7 @@
         <v>0.8771929824561403</v>
       </c>
       <c r="C59" t="n">
-        <v>0.7237183553474669</v>
+        <v>0.8383133836136275</v>
       </c>
     </row>
     <row r="60">
@@ -1091,7 +1091,7 @@
         <v>0.8620689655172414</v>
       </c>
       <c r="C60" t="n">
-        <v>0.6991855700766473</v>
+        <v>0.8268523418079029</v>
       </c>
     </row>
     <row r="61">
@@ -1102,7 +1102,7 @@
         <v>0.8474576271186441</v>
       </c>
       <c r="C61" t="n">
-        <v>0.6682620667752242</v>
+        <v>0.7993885688728571</v>
       </c>
     </row>
     <row r="62">
@@ -1113,7 +1113,7 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="C62" t="n">
-        <v>0.6377607114602859</v>
+        <v>0.763767669019116</v>
       </c>
     </row>
     <row r="63">
@@ -1124,7 +1124,7 @@
         <v>0.819672131147541</v>
       </c>
       <c r="C63" t="n">
-        <v>0.6178910122042283</v>
+        <v>0.7303082697916113</v>
       </c>
     </row>
     <row r="64">
@@ -1135,7 +1135,7 @@
         <v>0.8064516129032259</v>
       </c>
       <c r="C64" t="n">
-        <v>0.5960972781710523</v>
+        <v>0.6898064499989867</v>
       </c>
     </row>
     <row r="65">
@@ -1146,7 +1146,7 @@
         <v>0.7936507936507936</v>
       </c>
       <c r="C65" t="n">
-        <v>0.5715772445228667</v>
+        <v>0.6602599864652404</v>
       </c>
     </row>
     <row r="66">
@@ -1157,7 +1157,7 @@
         <v>0.78125</v>
       </c>
       <c r="C66" t="n">
-        <v>0.5453958649190287</v>
+        <v>0.6294007105353674</v>
       </c>
     </row>
     <row r="67">
@@ -1168,7 +1168,7 @@
         <v>0.7692307692307692</v>
       </c>
       <c r="C67" t="n">
-        <v>0.5247774530055727</v>
+        <v>0.6043501561073117</v>
       </c>
     </row>
     <row r="68">
@@ -1179,7 +1179,7 @@
         <v>0.7575757575757576</v>
       </c>
       <c r="C68" t="n">
-        <v>0.5077269473841866</v>
+        <v>0.5831105921573437</v>
       </c>
     </row>
     <row r="69">
@@ -1190,7 +1190,7 @@
         <v>0.7462686567164178</v>
       </c>
       <c r="C69" t="n">
-        <v>0.4887248183474932</v>
+        <v>0.5601438217271778</v>
       </c>
     </row>
     <row r="70">
@@ -1201,7 +1201,7 @@
         <v>0.7352941176470588</v>
       </c>
       <c r="C70" t="n">
-        <v>0.468822017056019</v>
+        <v>0.5362999186615098</v>
       </c>
     </row>
     <row r="71">
@@ -1212,7 +1212,7 @@
         <v>0.7246376811594202</v>
       </c>
       <c r="C71" t="n">
-        <v>0.454902583459698</v>
+        <v>0.5184595366674053</v>
       </c>
     </row>
     <row r="72">
@@ -1223,7 +1223,7 @@
         <v>0.7142857142857142</v>
       </c>
       <c r="C72" t="n">
-        <v>0.442260508880316</v>
+        <v>0.5020958584853978</v>
       </c>
     </row>
     <row r="73">
@@ -1234,7 +1234,7 @@
         <v>0.7042253521126761</v>
       </c>
       <c r="C73" t="n">
-        <v>0.430022954664794</v>
+        <v>0.4866673702615056</v>
       </c>
     </row>
     <row r="74">
@@ -1245,7 +1245,7 @@
         <v>0.6944444444444444</v>
       </c>
       <c r="C74" t="n">
-        <v>0.418163288124916</v>
+        <v>0.4725859379634039</v>
       </c>
     </row>
     <row r="75">
@@ -1256,7 +1256,7 @@
         <v>0.684931506849315</v>
       </c>
       <c r="C75" t="n">
-        <v>0.4069869929039572</v>
+        <v>0.4592515736681698</v>
       </c>
     </row>
     <row r="76">
@@ -1267,7 +1267,7 @@
         <v>0.6756756756756757</v>
       </c>
       <c r="C76" t="n">
-        <v>0.3980862940294396</v>
+        <v>0.4480759128264587</v>
       </c>
     </row>
     <row r="77">
@@ -1278,7 +1278,7 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="C77" t="n">
-        <v>0.3894801290482373</v>
+        <v>0.4371892062541298</v>
       </c>
     </row>
     <row r="78">
@@ -1289,7 +1289,7 @@
         <v>0.6578947368421053</v>
       </c>
       <c r="C78" t="n">
-        <v>0.381177514438206</v>
+        <v>0.4265857649437031</v>
       </c>
     </row>
     <row r="79">
@@ -1300,7 +1300,7 @@
         <v>0.6493506493506493</v>
       </c>
       <c r="C79" t="n">
-        <v>0.3731917989044305</v>
+        <v>0.4162589068395498</v>
       </c>
     </row>
     <row r="80">
@@ -1311,7 +1311,7 @@
         <v>0.641025641025641</v>
       </c>
       <c r="C80" t="n">
-        <v>0.365536189827644</v>
+        <v>0.4062010789248511</v>
       </c>
     </row>
     <row r="81">
@@ -1322,7 +1322,7 @@
         <v>0.6329113924050632</v>
       </c>
       <c r="C81" t="n">
-        <v>0.3582000387412106</v>
+        <v>0.396404030670876</v>
       </c>
     </row>
     <row r="82">
@@ -1333,7 +1333,7 @@
         <v>0.625</v>
       </c>
       <c r="C82" t="n">
-        <v>0.3511330468463968</v>
+        <v>0.3868651774118748</v>
       </c>
     </row>
     <row r="83">
@@ -1344,7 +1344,7 @@
         <v>0.6172839506172839</v>
       </c>
       <c r="C83" t="n">
-        <v>0.3442666525102255</v>
+        <v>0.3775849668065719</v>
       </c>
     </row>
     <row r="84">
@@ -1355,7 +1355,7 @@
         <v>0.6097560975609756</v>
       </c>
       <c r="C84" t="n">
-        <v>0.3375364837563116</v>
+        <v>0.3685364100460648</v>
       </c>
     </row>
     <row r="85">
@@ -1366,7 +1366,7 @@
         <v>0.6024096385542168</v>
       </c>
       <c r="C85" t="n">
-        <v>0.3308879642638029</v>
+        <v>0.359711019594353</v>
       </c>
     </row>
     <row r="86">
@@ -1377,7 +1377,7 @@
         <v>0.5952380952380952</v>
       </c>
       <c r="C86" t="n">
-        <v>0.3242298386035689</v>
+        <v>0.3511008399012442</v>
       </c>
     </row>
     <row r="87">
@@ -1388,7 +1388,7 @@
         <v>0.5882352941176471</v>
       </c>
       <c r="C87" t="n">
-        <v>0.3175397257372117</v>
+        <v>0.3426986573487129</v>
       </c>
     </row>
     <row r="88">
@@ -1399,7 +1399,7 @@
         <v>0.5813953488372093</v>
       </c>
       <c r="C88" t="n">
-        <v>0.3107596573391609</v>
+        <v>0.334498159920655</v>
       </c>
     </row>
     <row r="89">
@@ -1410,7 +1410,7 @@
         <v>0.5747126436781609</v>
       </c>
       <c r="C89" t="n">
-        <v>0.3039019365675392</v>
+        <v>0.3273842893477041</v>
       </c>
     </row>
     <row r="90">
@@ -1421,7 +1421,7 @@
         <v>0.5681818181818182</v>
       </c>
       <c r="C90" t="n">
-        <v>0.2969568961954478</v>
+        <v>0.3205612229975925</v>
       </c>
     </row>
     <row r="91">
@@ -1432,7 +1432,7 @@
         <v>0.5617977528089888</v>
       </c>
       <c r="C91" t="n">
-        <v>0.29009686493448</v>
+        <v>0.315170301903336</v>
       </c>
     </row>
     <row r="92">
@@ -1443,7 +1443,7 @@
         <v>0.5555555555555556</v>
       </c>
       <c r="C92" t="n">
-        <v>0.2842135431486375</v>
+        <v>0.3097887941136148</v>
       </c>
     </row>
     <row r="93">
@@ -1454,7 +1454,7 @@
         <v>0.5494505494505494</v>
       </c>
       <c r="C93" t="n">
-        <v>0.279218948081674</v>
+        <v>0.3042420763946727</v>
       </c>
     </row>
     <row r="94">
@@ -1465,7 +1465,7 @@
         <v>0.5434782608695652</v>
       </c>
       <c r="C94" t="n">
-        <v>0.2744027944385423</v>
+        <v>0.2985334764371539</v>
       </c>
     </row>
     <row r="95">
@@ -1476,7 +1476,7 @@
         <v>0.5376344086021505</v>
       </c>
       <c r="C95" t="n">
-        <v>0.269490477364792</v>
+        <v>0.29266000675161</v>
       </c>
     </row>
     <row r="96">
@@ -1487,7 +1487,7 @@
         <v>0.5319148936170213</v>
       </c>
       <c r="C96" t="n">
-        <v>0.2645123327772841</v>
+        <v>0.2865964664549759</v>
       </c>
     </row>
     <row r="97">
@@ -1498,7 +1498,7 @@
         <v>0.5263157894736842</v>
       </c>
       <c r="C97" t="n">
-        <v>0.2594698931108881</v>
+        <v>0.2803460568432749</v>
       </c>
     </row>
     <row r="98">
@@ -1509,7 +1509,7 @@
         <v>0.5208333333333334</v>
       </c>
       <c r="C98" t="n">
-        <v>0.2543833337039801</v>
+        <v>0.2739386441257155</v>
       </c>
     </row>
     <row r="99">
@@ -1520,7 +1520,7 @@
         <v>0.5154639175257733</v>
       </c>
       <c r="C99" t="n">
-        <v>0.2492878510403196</v>
+        <v>0.2678056948149313</v>
       </c>
     </row>
     <row r="100">
@@ -1531,7 +1531,7 @@
         <v>0.5102040816326531</v>
       </c>
       <c r="C100" t="n">
-        <v>0.2441887539554189</v>
+        <v>0.2618199283544293</v>
       </c>
     </row>
     <row r="101">
@@ -1542,7 +1542,7 @@
         <v>0.5050505050505051</v>
       </c>
       <c r="C101" t="n">
-        <v>0.2391199007448934</v>
+        <v>0.2557709148406225</v>
       </c>
     </row>
     <row r="102">
@@ -1553,7 +1553,7 @@
         <v>0.5</v>
       </c>
       <c r="C102" t="n">
-        <v>0.2340964752139003</v>
+        <v>0.2496822459309662</v>
       </c>
     </row>
     <row r="103">
@@ -1564,7 +1564,7 @@
         <v>0.495049504950495</v>
       </c>
       <c r="C103" t="n">
-        <v>0.2291302399136178</v>
+        <v>0.2435899316452447</v>
       </c>
     </row>
     <row r="104">
@@ -1575,7 +1575,7 @@
         <v>0.4901960784313725</v>
       </c>
       <c r="C104" t="n">
-        <v>0.2242475192530521</v>
+        <v>0.2375160585445454</v>
       </c>
     </row>
     <row r="105">
@@ -1586,7 +1586,7 @@
         <v>0.4854368932038835</v>
       </c>
       <c r="C105" t="n">
-        <v>0.2194489296412251</v>
+        <v>0.2314885690323058</v>
       </c>
     </row>
     <row r="106">
@@ -1597,7 +1597,7 @@
         <v>0.4807692307692307</v>
       </c>
       <c r="C106" t="n">
-        <v>0.2147503007932816</v>
+        <v>0.2266374170791238</v>
       </c>
     </row>
     <row r="107">
@@ -1608,7 +1608,7 @@
         <v>0.4761904761904762</v>
       </c>
       <c r="C107" t="n">
-        <v>0.2101876634244539</v>
+        <v>0.2236228155899974</v>
       </c>
     </row>
     <row r="108">
@@ -1619,7 +1619,7 @@
         <v>0.4716981132075471</v>
       </c>
       <c r="C108" t="n">
-        <v>0.2059766241928694</v>
+        <v>0.2210800641165077</v>
       </c>
     </row>
     <row r="109">
@@ -1630,7 +1630,7 @@
         <v>0.4672897196261682</v>
       </c>
       <c r="C109" t="n">
-        <v>0.2023893260696357</v>
+        <v>0.2184849612116776</v>
       </c>
     </row>
     <row r="110">
@@ -1641,7 +1641,7 @@
         <v>0.4629629629629629</v>
       </c>
       <c r="C110" t="n">
-        <v>0.1988779758385557</v>
+        <v>0.2158272523867166</v>
       </c>
     </row>
     <row r="111">
@@ -1652,7 +1652,7 @@
         <v>0.4587155963302752</v>
       </c>
       <c r="C111" t="n">
-        <v>0.1954415997467808</v>
+        <v>0.2131029029847054</v>
       </c>
     </row>
     <row r="112">
@@ -1663,7 +1663,7 @@
         <v>0.4545454545454545</v>
       </c>
       <c r="C112" t="n">
-        <v>0.1920811387400201</v>
+        <v>0.2103110711691426</v>
       </c>
     </row>
     <row r="113">
@@ -1674,7 +1674,7 @@
         <v>0.4504504504504504</v>
       </c>
       <c r="C113" t="n">
-        <v>0.1887924281077063</v>
+        <v>0.2074536366712818</v>
       </c>
     </row>
     <row r="114">
@@ -1685,7 +1685,7 @@
         <v>0.4464285714285714</v>
       </c>
       <c r="C114" t="n">
-        <v>0.1858248899558066</v>
+        <v>0.2045347117831452</v>
       </c>
     </row>
     <row r="115">
@@ -1696,7 +1696,7 @@
         <v>0.4424778761061947</v>
       </c>
       <c r="C115" t="n">
-        <v>0.1829494586930759</v>
+        <v>0.2015606991108581</v>
       </c>
     </row>
     <row r="116">
@@ -1707,7 +1707,7 @@
         <v>0.4385964912280702</v>
       </c>
       <c r="C116" t="n">
-        <v>0.180137513506511</v>
+        <v>0.1985497888844205</v>
       </c>
     </row>
     <row r="117">
@@ -1718,7 +1718,7 @@
         <v>0.4347826086956521</v>
       </c>
       <c r="C117" t="n">
-        <v>0.1773848272141608</v>
+        <v>0.1954977267748401</v>
       </c>
     </row>
     <row r="118">
@@ -1729,7 +1729,7 @@
         <v>0.4310344827586207</v>
       </c>
       <c r="C118" t="n">
-        <v>0.1746872518967459</v>
+        <v>0.1924129513099939</v>
       </c>
     </row>
     <row r="119">
@@ -1740,7 +1740,7 @@
         <v>0.4273504273504274</v>
       </c>
       <c r="C119" t="n">
-        <v>0.1720407964606915</v>
+        <v>0.1893041239122806</v>
       </c>
     </row>
     <row r="120">
@@ -1751,7 +1751,7 @@
         <v>0.4237288135593221</v>
       </c>
       <c r="C120" t="n">
-        <v>0.1694416905577522</v>
+        <v>0.186179864341764</v>
       </c>
     </row>
     <row r="121">
@@ -1762,7 +1762,7 @@
         <v>0.4201680672268908</v>
       </c>
       <c r="C121" t="n">
-        <v>0.1668864348636357</v>
+        <v>0.1830485393335846</v>
       </c>
     </row>
     <row r="122">
@@ -1773,7 +1773,7 @@
         <v>0.4166666666666667</v>
       </c>
       <c r="C122" t="n">
-        <v>0.1643718382718428</v>
+        <v>0.1799181013084816</v>
       </c>
     </row>
     <row r="123">
@@ -1784,7 +1784,7 @@
         <v>0.4132231404958678</v>
       </c>
       <c r="C123" t="n">
-        <v>0.1618950428593282</v>
+        <v>0.1767959725441482</v>
       </c>
     </row>
     <row r="124">
@@ -1795,7 +1795,7 @@
         <v>0.4098360655737705</v>
       </c>
       <c r="C124" t="n">
-        <v>0.1594535377565672</v>
+        <v>0.1736889693546669</v>
       </c>
     </row>
     <row r="125">
@@ -1806,7 +1806,7 @@
         <v>0.4065040650406504</v>
       </c>
       <c r="C125" t="n">
-        <v>0.1570451631845396</v>
+        <v>0.1706032603565771</v>
       </c>
     </row>
     <row r="126">
@@ -1817,7 +1817,7 @@
         <v>0.4032258064516129</v>
       </c>
       <c r="C126" t="n">
-        <v>0.1546681060269992</v>
+        <v>0.1675443528859728</v>
       </c>
     </row>
     <row r="127">
@@ -1828,7 +1828,7 @@
         <v>0.4</v>
       </c>
       <c r="C127" t="n">
-        <v>0.1523208882912999</v>
+        <v>0.1645210801809427</v>
       </c>
     </row>
     <row r="128">
@@ -1839,7 +1839,7 @@
         <v>0.3968253968253968</v>
       </c>
       <c r="C128" t="n">
-        <v>0.150002349813928</v>
+        <v>0.1615329672326155</v>
       </c>
     </row>
     <row r="129">
@@ -1850,7 +1850,7 @@
         <v>0.3937007874015748</v>
       </c>
       <c r="C129" t="n">
-        <v>0.1477116264712651</v>
+        <v>0.1585836602849597</v>
       </c>
     </row>
     <row r="130">
@@ -1861,7 +1861,7 @@
         <v>0.390625</v>
       </c>
       <c r="C130" t="n">
-        <v>0.1454481250697862</v>
+        <v>0.1556763086742081</v>
       </c>
     </row>
     <row r="131">
@@ -1872,7 +1872,7 @@
         <v>0.3875968992248062</v>
       </c>
       <c r="C131" t="n">
-        <v>0.1432114959837913</v>
+        <v>0.1528135693511132</v>
       </c>
     </row>
     <row r="132">
@@ -1883,7 +1883,7 @@
         <v>0.3846153846153846</v>
       </c>
       <c r="C132" t="n">
-        <v>0.1410016185218426</v>
+        <v>0.149997672769097</v>
       </c>
     </row>
     <row r="133">
@@ -1894,7 +1894,7 @@
         <v>0.3816793893129771</v>
       </c>
       <c r="C133" t="n">
-        <v>0.1388192159533398</v>
+        <v>0.1472311185896536</v>
       </c>
     </row>
     <row r="134">
@@ -1905,7 +1905,7 @@
         <v>0.3787878787878788</v>
       </c>
       <c r="C134" t="n">
-        <v>0.1366638289277</v>
+        <v>0.1445147274941867</v>
       </c>
     </row>
     <row r="135">
@@ -1916,7 +1916,7 @@
         <v>0.3759398496240601</v>
       </c>
       <c r="C135" t="n">
-        <v>0.1345357951850283</v>
+        <v>0.1418496951650787</v>
       </c>
     </row>
     <row r="136">
@@ -1927,7 +1927,7 @@
         <v>0.3731343283582089</v>
       </c>
       <c r="C136" t="n">
-        <v>0.1324355539204029</v>
+        <v>0.1392369655084443</v>
       </c>
     </row>
     <row r="137">
@@ -1938,7 +1938,7 @@
         <v>0.3703703703703703</v>
       </c>
       <c r="C137" t="n">
-        <v>0.1303830118340421</v>
+        <v>0.1366772678473701</v>
       </c>
     </row>
     <row r="138">
@@ -1949,7 +1949,7 @@
         <v>0.3676470588235294</v>
       </c>
       <c r="C138" t="n">
-        <v>0.1287109089957128</v>
+        <v>0.1341771402575433</v>
       </c>
     </row>
     <row r="139">
@@ -1960,7 +1960,7 @@
         <v>0.364963503649635</v>
       </c>
       <c r="C139" t="n">
-        <v>0.1269791020148727</v>
+        <v>0.1317309249819986</v>
       </c>
     </row>
     <row r="140">
@@ -1971,7 +1971,7 @@
         <v>0.3623188405797101</v>
       </c>
       <c r="C140" t="n">
-        <v>0.1251798270734296</v>
+        <v>0.1293387904886005</v>
       </c>
     </row>
     <row r="141">
@@ -1982,7 +1982,7 @@
         <v>0.3597122302158273</v>
       </c>
       <c r="C141" t="n">
-        <v>0.1237647458976231</v>
+        <v>0.1270008889858447</v>
       </c>
     </row>
     <row r="142">
@@ -1993,7 +1993,7 @@
         <v>0.3571428571428571</v>
       </c>
       <c r="C142" t="n">
-        <v>0.1224106272928428</v>
+        <v>0.124920622327576</v>
       </c>
     </row>
     <row r="143">
@@ -2004,7 +2004,7 @@
         <v>0.3546099290780142</v>
       </c>
       <c r="C143" t="n">
-        <v>0.1209965321179503</v>
+        <v>0.1230839450769079</v>
       </c>
     </row>
     <row r="144">
@@ -2015,7 +2015,7 @@
         <v>0.3521126760563381</v>
       </c>
       <c r="C144" t="n">
-        <v>0.1195085166047825</v>
+        <v>0.121283439137238</v>
       </c>
     </row>
     <row r="145">
@@ -2026,7 +2026,7 @@
         <v>0.3496503496503497</v>
       </c>
       <c r="C145" t="n">
-        <v>0.1179442383295577</v>
+        <v>0.1195185809459513</v>
       </c>
     </row>
     <row r="146">
@@ -2037,7 +2037,7 @@
         <v>0.3472222222222222</v>
       </c>
       <c r="C146" t="n">
-        <v>0.1163154600389245</v>
+        <v>0.1177915955164335</v>
       </c>
     </row>
     <row r="147">
@@ -2048,7 +2048,7 @@
         <v>0.3448275862068966</v>
       </c>
       <c r="C147" t="n">
-        <v>0.1147033870577248</v>
+        <v>0.1161011979232936</v>
       </c>
     </row>
     <row r="148">
@@ -2059,7 +2059,7 @@
         <v>0.3424657534246575</v>
       </c>
       <c r="C148" t="n">
-        <v>0.11326296511777</v>
+        <v>0.1144447696803025</v>
       </c>
     </row>
     <row r="149">
@@ -2070,7 +2070,7 @@
         <v>0.3401360544217687</v>
       </c>
       <c r="C149" t="n">
-        <v>0.1118077644813729</v>
+        <v>0.1128217699336572</v>
       </c>
     </row>
     <row r="150">
@@ -2081,7 +2081,7 @@
         <v>0.3378378378378378</v>
       </c>
       <c r="C150" t="n">
-        <v>0.1103370149884912</v>
+        <v>0.1112316496773201</v>
       </c>
     </row>
     <row r="151">
@@ -2092,7 +2092,7 @@
         <v>0.3355704697986577</v>
       </c>
       <c r="C151" t="n">
-        <v>0.1088532731181895</v>
+        <v>0.109673851285032</v>
       </c>
     </row>
     <row r="152">
@@ -2103,7 +2103,7 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="C152" t="n">
-        <v>0.1073614011176534</v>
+        <v>0.108147808451366</v>
       </c>
     </row>
     <row r="153">
@@ -2114,7 +2114,7 @@
         <v>0.3311258278145696</v>
       </c>
       <c r="C153" t="n">
-        <v>0.1058650375848483</v>
+        <v>0.1066529464860421</v>
       </c>
     </row>
     <row r="154">
@@ -2125,7 +2125,7 @@
         <v>0.3289473684210527</v>
       </c>
       <c r="C154" t="n">
-        <v>0.104364748435589</v>
+        <v>0.105188682904591</v>
       </c>
     </row>
     <row r="155">
@@ -2136,7 +2136,7 @@
         <v>0.326797385620915</v>
       </c>
       <c r="C155" t="n">
-        <v>0.1028639106520703</v>
+        <v>0.1037544282322953</v>
       </c>
     </row>
     <row r="156">
@@ -2147,7 +2147,7 @@
         <v>0.3246753246753247</v>
       </c>
       <c r="C156" t="n">
-        <v>0.1013659108150026</v>
+        <v>0.1023495870096892</v>
       </c>
     </row>
     <row r="157">
@@ -2158,7 +2158,7 @@
         <v>0.3225806451612903</v>
       </c>
       <c r="C157" t="n">
-        <v>0.09987407961942159</v>
+        <v>0.1009735589078728</v>
       </c>
     </row>
     <row r="158">
@@ -2169,7 +2169,7 @@
         <v>0.3205128205128205</v>
       </c>
       <c r="C158" t="n">
-        <v>0.09839379203810639</v>
+        <v>0.099625739959694</v>
       </c>
     </row>
     <row r="159">
@@ -2180,7 +2180,7 @@
         <v>0.3184713375796178</v>
       </c>
       <c r="C159" t="n">
-        <v>0.09721398871822416</v>
+        <v>0.09830552383035332</v>
       </c>
     </row>
     <row r="160">
@@ -2191,7 +2191,7 @@
         <v>0.3164556962025316</v>
       </c>
       <c r="C160" t="n">
-        <v>0.09603646492626217</v>
+        <v>0.09701230313368658</v>
       </c>
     </row>
     <row r="161">
@@ -2202,7 +2202,7 @@
         <v>0.3144654088050314</v>
       </c>
       <c r="C161" t="n">
-        <v>0.09484172796445757</v>
+        <v>0.0957454707296049</v>
       </c>
     </row>
     <row r="162">
@@ -2213,7 +2213,7 @@
         <v>0.3125</v>
       </c>
       <c r="C162" t="n">
-        <v>0.09363331814128512</v>
+        <v>0.09450442102318538</v>
       </c>
     </row>
     <row r="163">
@@ -2224,7 +2224,7 @@
         <v>0.3105590062111801</v>
       </c>
       <c r="C163" t="n">
-        <v>0.0924148780332735</v>
+        <v>0.09328855120830588</v>
       </c>
     </row>
     <row r="164">
@@ -2235,7 +2235,7 @@
         <v>0.308641975308642</v>
       </c>
       <c r="C164" t="n">
-        <v>0.0911901266089753</v>
+        <v>0.09209726247232175</v>
       </c>
     </row>
     <row r="165">
@@ -2246,7 +2246,7 @@
         <v>0.3067484662576687</v>
       </c>
       <c r="C165" t="n">
-        <v>0.08996607091463495</v>
+        <v>0.09092996112778429</v>
       </c>
     </row>
     <row r="166">
@@ -2257,7 +2257,7 @@
         <v>0.3048780487804878</v>
       </c>
       <c r="C166" t="n">
-        <v>0.08874239029348983</v>
+        <v>0.08978605967463102</v>
       </c>
     </row>
     <row r="167">
@@ -2268,7 +2268,7 @@
         <v>0.303030303030303</v>
       </c>
       <c r="C167" t="n">
-        <v>0.08767209700668394</v>
+        <v>0.08866497778628266</v>
       </c>
     </row>
     <row r="168">
@@ -2279,7 +2279,7 @@
         <v>0.3012048192771084</v>
       </c>
       <c r="C168" t="n">
-        <v>0.08661459054915153</v>
+        <v>0.08756614320938047</v>
       </c>
     </row>
     <row r="169">
@@ -2290,7 +2290,7 @@
         <v>0.2994011976047904</v>
       </c>
       <c r="C169" t="n">
-        <v>0.0855620176818067</v>
+        <v>0.0864891582519879</v>
       </c>
     </row>
     <row r="170">
@@ -2301,7 +2301,7 @@
         <v>0.2976190476190476</v>
       </c>
       <c r="C170" t="n">
-        <v>0.08451792491313226</v>
+        <v>0.08543708759602615</v>
       </c>
     </row>
     <row r="171">
@@ -2312,7 +2312,7 @@
         <v>0.2958579881656805</v>
       </c>
       <c r="C171" t="n">
-        <v>0.08348372363888028</v>
+        <v>0.08440748759991565</v>
       </c>
     </row>
     <row r="172">
@@ -2323,7 +2323,7 @@
         <v>0.2941176470588235</v>
       </c>
       <c r="C172" t="n">
-        <v>0.08246084520662506</v>
+        <v>0.08342077327255791</v>
       </c>
     </row>
     <row r="173">
@@ -2334,7 +2334,7 @@
         <v>0.2923976608187134</v>
       </c>
       <c r="C173" t="n">
-        <v>0.08144869486402966</v>
+        <v>0.08250847478893686</v>
       </c>
     </row>
     <row r="174">
@@ -2345,7 +2345,7 @@
         <v>0.2906976744186047</v>
       </c>
       <c r="C174" t="n">
-        <v>0.0804484966585611</v>
+        <v>0.08161221174992103</v>
       </c>
     </row>
     <row r="175">
@@ -2356,7 +2356,7 @@
         <v>0.2890173410404624</v>
       </c>
       <c r="C175" t="n">
-        <v>0.07946846887882994</v>
+        <v>0.08073159025488703</v>
       </c>
     </row>
     <row r="176">
@@ -2367,7 +2367,7 @@
         <v>0.2873563218390804</v>
       </c>
       <c r="C176" t="n">
-        <v>0.07856092692709904</v>
+        <v>0.07986622361168171</v>
       </c>
     </row>
     <row r="177">
@@ -2378,7 +2378,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="C177" t="n">
-        <v>0.07766665152579845</v>
+        <v>0.07901573284965389</v>
       </c>
     </row>
     <row r="178">
@@ -2389,7 +2389,7 @@
         <v>0.2840909090909091</v>
       </c>
       <c r="C178" t="n">
-        <v>0.07678581388983101</v>
+        <v>0.07817974715523146</v>
       </c>
     </row>
     <row r="179">
@@ -2400,7 +2400,7 @@
         <v>0.2824858757062147</v>
       </c>
       <c r="C179" t="n">
-        <v>0.07591854608690396</v>
+        <v>0.07735790422238065</v>
       </c>
     </row>
     <row r="180">
@@ -2411,7 +2411,7 @@
         <v>0.2808988764044944</v>
       </c>
       <c r="C180" t="n">
-        <v>0.07506494180023379</v>
+        <v>0.07654985054369572</v>
       </c>
     </row>
     <row r="181">
@@ -2422,7 +2422,7 @@
         <v>0.2793296089385475</v>
       </c>
       <c r="C181" t="n">
-        <v>0.07422675684586508</v>
+        <v>0.07575694102573181</v>
       </c>
     </row>
     <row r="182">
@@ -2433,7 +2433,7 @@
         <v>0.2777777777777778</v>
       </c>
       <c r="C182" t="n">
-        <v>0.07340357858765076</v>
+        <v>0.07497840713351565</v>
       </c>
     </row>
     <row r="183">
@@ -2444,7 +2444,7 @@
         <v>0.2762430939226519</v>
       </c>
       <c r="C183" t="n">
-        <v>0.07259405954926737</v>
+        <v>0.07421258892679673</v>
       </c>
     </row>
     <row r="184">
@@ -2455,7 +2455,7 @@
         <v>0.2747252747252747</v>
       </c>
       <c r="C184" t="n">
-        <v>0.07179815564810925</v>
+        <v>0.07345917146792402</v>
       </c>
     </row>
     <row r="185">
@@ -2466,7 +2466,7 @@
         <v>0.273224043715847</v>
       </c>
       <c r="C185" t="n">
-        <v>0.07101579250147978</v>
+        <v>0.07271784910428067</v>
       </c>
     </row>
     <row r="186">
@@ -2477,7 +2477,7 @@
         <v>0.2717391304347826</v>
       </c>
       <c r="C186" t="n">
-        <v>0.07024686757025123</v>
+        <v>0.07198832543358974</v>
       </c>
     </row>
     <row r="187">
@@ -2488,7 +2488,7 @@
         <v>0.2702702702702702</v>
       </c>
       <c r="C187" t="n">
-        <v>0.06949125237353757</v>
+        <v>0.0712703132327718</v>
       </c>
     </row>
     <row r="188">
@@ -2499,7 +2499,7 @@
         <v>0.2688172043010753</v>
       </c>
       <c r="C188" t="n">
-        <v>0.06874970491302602</v>
+        <v>0.07056353435447563</v>
       </c>
     </row>
     <row r="189">
@@ -2510,7 +2510,7 @@
         <v>0.267379679144385</v>
       </c>
       <c r="C189" t="n">
-        <v>0.06804002130866735</v>
+        <v>0.06986771958927847</v>
       </c>
     </row>
     <row r="190">
@@ -2521,7 +2521,7 @@
         <v>0.2659574468085106</v>
       </c>
       <c r="C190" t="n">
-        <v>0.06734270426983953</v>
+        <v>0.06918260851598035</v>
       </c>
     </row>
     <row r="191">
@@ -2532,7 +2532,7 @@
         <v>0.2645502645502645</v>
       </c>
       <c r="C191" t="n">
-        <v>0.06665749875130045</v>
+        <v>0.06850794931873311</v>
       </c>
     </row>
     <row r="192">
@@ -2543,7 +2543,7 @@
         <v>0.2631578947368421</v>
       </c>
       <c r="C192" t="n">
-        <v>0.06598415346506696</v>
+        <v>0.06784349859373008</v>
       </c>
     </row>
     <row r="193">
@@ -2554,7 +2554,7 @@
         <v>0.2617801047120419</v>
       </c>
       <c r="C193" t="n">
-        <v>0.06532242098821427</v>
+        <v>0.06718902113787663</v>
       </c>
     </row>
     <row r="194">
@@ -2565,7 +2565,7 @@
         <v>0.2604166666666667</v>
       </c>
       <c r="C194" t="n">
-        <v>0.06467205785676552</v>
+        <v>0.06654428972797888</v>
       </c>
     </row>
     <row r="195">
@@ -2576,7 +2576,7 @@
         <v>0.2590673575129534</v>
       </c>
       <c r="C195" t="n">
-        <v>0.06403282464303885</v>
+        <v>0.06590908489102816</v>
       </c>
     </row>
     <row r="196">
@@ -2587,7 +2587,7 @@
         <v>0.2577319587628866</v>
       </c>
       <c r="C196" t="n">
-        <v>0.06340448601200876</v>
+        <v>0.06528319466003864</v>
       </c>
     </row>
     <row r="197">
@@ -2598,7 +2598,7 @@
         <v>0.2564102564102564</v>
       </c>
       <c r="C197" t="n">
-        <v>0.06278681077569982</v>
+        <v>0.06466641433711545</v>
       </c>
     </row>
     <row r="198">
@@ -2609,7 +2609,7 @@
         <v>0.2551020408163265</v>
       </c>
       <c r="C198" t="n">
-        <v>0.06218035929798766</v>
+        <v>0.06405854624289448</v>
       </c>
     </row>
     <row r="199">
@@ -2620,7 +2620,7 @@
         <v>0.2538071065989848</v>
       </c>
       <c r="C199" t="n">
-        <v>0.06158578558075654</v>
+        <v>0.06357360329718552</v>
       </c>
     </row>
     <row r="200">
@@ -2631,7 +2631,7 @@
         <v>0.2525252525252525</v>
       </c>
       <c r="C200" t="n">
-        <v>0.06100116014685178</v>
+        <v>0.0631384235905947</v>
       </c>
     </row>
     <row r="201">
@@ -2642,7 +2642,7 @@
         <v>0.2512562814070352</v>
       </c>
       <c r="C201" t="n">
-        <v>0.06042626962425181</v>
+        <v>0.06270880585027419</v>
       </c>
     </row>
     <row r="202">
@@ -2653,7 +2653,7 @@
         <v>0.25</v>
       </c>
       <c r="C202" t="n">
-        <v>0.05986090483120173</v>
+        <v>0.06228444749667893</v>
       </c>
     </row>
   </sheetData>
